--- a/restaurant_crawler/restaurant_data_台北_牛排_20250910_192841_with_emails.xlsx
+++ b/restaurant_crawler/restaurant_data_台北_牛排_20250910_192841_with_emails.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\slow3\OneDrive\桌面\GitHubProjects\BYOB\restaurant_crawler\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AC8960A-CC93-4572-A238-D0A85D03D2AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89D8AC7B-BAAE-46C0-A568-A5554E2AB1C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="308">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="270">
   <si>
     <t>name</t>
   </si>
@@ -103,18 +103,6 @@
     <t>found</t>
   </si>
   <si>
-    <t>瀧厚炙燒熟成牛排 臺北.大安店</t>
-  </si>
-  <si>
-    <t>106台灣台北市大安區和平東路二段183號</t>
-  </si>
-  <si>
-    <t>02 2701 5885</t>
-  </si>
-  <si>
-    <t>ChIJMQTebJqrQjQR3p3Zb5ewRsk</t>
-  </si>
-  <si>
     <t>台北晶華酒店- ROBIN'S 牛排屋</t>
   </si>
   <si>
@@ -283,18 +271,6 @@
     <t>ChIJkT9RupupQjQROzXoveyqnmU</t>
   </si>
   <si>
-    <t>瀧厚炙燒熟成牛排 台北.北車店</t>
-  </si>
-  <si>
-    <t>100230台灣台北市中正區北平西路3號2樓</t>
-  </si>
-  <si>
-    <t>02 2311 0698</t>
-  </si>
-  <si>
-    <t>ChIJeZnryQ-pQjQRNnLc5C4JK8s</t>
-  </si>
-  <si>
     <t>茱莉金牛排餐酒館</t>
   </si>
   <si>
@@ -646,21 +622,6 @@
     <t>ChIJv5zxAdCrQjQRYpGCL-p9_zk</t>
   </si>
   <si>
-    <t>人从众厚切牛排(台北永春店)</t>
-  </si>
-  <si>
-    <t>110台灣台北市信義區忠孝東路五段396號</t>
-  </si>
-  <si>
-    <t>02 8786 0950</t>
-  </si>
-  <si>
-    <t>https://www.jencongzhong.com.tw/</t>
-  </si>
-  <si>
-    <t>ChIJ2wu4YpCrQjQRSL0V6MomlBI</t>
-  </si>
-  <si>
     <t>王品牛排 台北南京東店</t>
   </si>
   <si>
@@ -751,15 +712,6 @@
     <t>ChIJGfix9WSpQjQRt8-Hz1c_JCk</t>
   </si>
   <si>
-    <t>教父牛排餐飲 MUCHOYAKI</t>
-  </si>
-  <si>
-    <t>110台灣台北市信義區松壽路9號6樓</t>
-  </si>
-  <si>
-    <t>ChIJeVHXFdurQjQRVD6SKmn0sn0</t>
-  </si>
-  <si>
     <t>TASTY西堤牛排台北羅斯福店</t>
   </si>
   <si>
@@ -820,36 +772,6 @@
     <t>info@wildwood.com.tw</t>
   </si>
   <si>
-    <t>沾美藝術庭苑 Jimmy’s Garden</t>
-  </si>
-  <si>
-    <t>106台灣台北市大安區新生南路三段11巷5號</t>
-  </si>
-  <si>
-    <t>02 2368 1197</t>
-  </si>
-  <si>
-    <t>https://www.facebook.com/jimmysgarden1949/?fref=ts</t>
-  </si>
-  <si>
-    <t>ChIJD9U3C4epQjQR7idvQVJyAvY</t>
-  </si>
-  <si>
-    <t>jimmygallery1105@gmail.com</t>
-  </si>
-  <si>
-    <t>人从众厚切牛排(台北安居店)</t>
-  </si>
-  <si>
-    <t>106台灣台北市大安區安居街36號</t>
-  </si>
-  <si>
-    <t>02 2732 5367</t>
-  </si>
-  <si>
-    <t>ChIJzzAlKjeqQjQRXzDYx0qxOqM</t>
-  </si>
-  <si>
     <t>教父牛排 Top Cap Steakhouse</t>
   </si>
   <si>
@@ -883,30 +805,6 @@
     <t>ChIJA-dy15SrQjQRY85AKqSup6E</t>
   </si>
   <si>
-    <t>人从众厚切牛排(台北復興店)</t>
-  </si>
-  <si>
-    <t>10664台灣台北市大安區復興南路二段27號</t>
-  </si>
-  <si>
-    <t>02 2706 0668</t>
-  </si>
-  <si>
-    <t>ChIJvSeCr-yrQjQRca5yiuSP8LQ</t>
-  </si>
-  <si>
-    <t>瀧厚炙燒熟成牛排 台北.民生店</t>
-  </si>
-  <si>
-    <t>105台灣台北市松山區民生東路五段99號1樓</t>
-  </si>
-  <si>
-    <t>02 2761 0068</t>
-  </si>
-  <si>
-    <t>ChIJb61nBQmrQjQRSzjQlYaN8_Y</t>
-  </si>
-  <si>
     <t>【台北君悅酒店】Bel Air 寶艾西餐廳</t>
   </si>
   <si>
@@ -932,18 +830,6 @@
   </si>
   <si>
     <t>ChIJt7JDM4KrQjQRjbeuPqbQQ8A</t>
-  </si>
-  <si>
-    <t>人从众厚切牛排 台北科技大樓</t>
-  </si>
-  <si>
-    <t>106101台灣台北市大安區復興南路二段275號2樓</t>
-  </si>
-  <si>
-    <t>02 2701 9818</t>
-  </si>
-  <si>
-    <t>ChIJcSJ-RgCrQjQR2YuHjwCIm_w</t>
   </si>
 </sst>
 </file>
@@ -1322,7 +1208,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I61"/>
+  <dimension ref="A1:I60"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="40.375" customWidth="1"/>
@@ -1400,19 +1286,19 @@
         <v>29</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="E3">
-        <v>4.5999999999999996</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="F3">
-        <v>4245</v>
+        <v>2587</v>
       </c>
       <c r="G3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H3" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="I3" t="s">
         <v>26</v>
@@ -1420,28 +1306,28 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>31</v>
+        <v>72</v>
       </c>
       <c r="B4" t="s">
-        <v>32</v>
+        <v>73</v>
       </c>
       <c r="C4" t="s">
-        <v>33</v>
+        <v>74</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="E4">
-        <v>4.4000000000000004</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="F4">
-        <v>2587</v>
+        <v>6738</v>
       </c>
       <c r="G4" t="s">
-        <v>35</v>
+        <v>76</v>
       </c>
       <c r="H4" t="s">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="I4" t="s">
         <v>26</v>
@@ -1449,28 +1335,28 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="B5" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="C5" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="E5">
-        <v>4.5999999999999996</v>
+        <v>4.5</v>
       </c>
       <c r="F5">
-        <v>6738</v>
+        <v>1771</v>
       </c>
       <c r="G5" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="H5" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="I5" t="s">
         <v>26</v>
@@ -1478,28 +1364,28 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="B6" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="C6" t="s">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>23</v>
+        <v>106</v>
       </c>
       <c r="E6">
-        <v>4.5999999999999996</v>
+        <v>4.2</v>
       </c>
       <c r="F6">
-        <v>6220</v>
+        <v>4469</v>
       </c>
       <c r="G6" t="s">
-        <v>90</v>
+        <v>107</v>
       </c>
       <c r="H6" t="s">
-        <v>25</v>
+        <v>108</v>
       </c>
       <c r="I6" t="s">
         <v>26</v>
@@ -1507,28 +1393,28 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>91</v>
+        <v>144</v>
       </c>
       <c r="B7" t="s">
-        <v>92</v>
+        <v>145</v>
       </c>
       <c r="C7" t="s">
-        <v>93</v>
+        <v>146</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>94</v>
+        <v>147</v>
       </c>
       <c r="E7">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="F7">
-        <v>1771</v>
+        <v>2018</v>
       </c>
       <c r="G7" t="s">
-        <v>95</v>
+        <v>148</v>
       </c>
       <c r="H7" t="s">
-        <v>96</v>
+        <v>149</v>
       </c>
       <c r="I7" t="s">
         <v>26</v>
@@ -1536,28 +1422,28 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>111</v>
+        <v>168</v>
       </c>
       <c r="B8" t="s">
-        <v>112</v>
+        <v>169</v>
       </c>
       <c r="C8" t="s">
-        <v>113</v>
+        <v>170</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>114</v>
+        <v>171</v>
       </c>
       <c r="E8">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="F8">
-        <v>4469</v>
+        <v>4412</v>
       </c>
       <c r="G8" t="s">
-        <v>115</v>
+        <v>172</v>
       </c>
       <c r="H8" t="s">
-        <v>116</v>
+        <v>173</v>
       </c>
       <c r="I8" t="s">
         <v>26</v>
@@ -1565,28 +1451,28 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>152</v>
+        <v>179</v>
       </c>
       <c r="B9" t="s">
-        <v>153</v>
+        <v>180</v>
       </c>
       <c r="C9" t="s">
-        <v>154</v>
+        <v>181</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>155</v>
+        <v>182</v>
       </c>
       <c r="E9">
-        <v>4.3</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="F9">
-        <v>2018</v>
+        <v>1657</v>
       </c>
       <c r="G9" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="H9" t="s">
-        <v>157</v>
+        <v>184</v>
       </c>
       <c r="I9" t="s">
         <v>26</v>
@@ -1594,28 +1480,28 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>176</v>
+        <v>208</v>
       </c>
       <c r="B10" t="s">
-        <v>177</v>
+        <v>209</v>
       </c>
       <c r="C10" t="s">
-        <v>178</v>
+        <v>210</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>179</v>
+        <v>211</v>
       </c>
       <c r="E10">
-        <v>4.5</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="F10">
-        <v>4412</v>
+        <v>636</v>
       </c>
       <c r="G10" t="s">
-        <v>180</v>
+        <v>212</v>
       </c>
       <c r="H10" t="s">
-        <v>181</v>
+        <v>213</v>
       </c>
       <c r="I10" t="s">
         <v>26</v>
@@ -1623,28 +1509,28 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>187</v>
+        <v>219</v>
       </c>
       <c r="B11" t="s">
-        <v>188</v>
+        <v>220</v>
       </c>
       <c r="C11" t="s">
-        <v>189</v>
+        <v>221</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>190</v>
+        <v>222</v>
       </c>
       <c r="E11">
         <v>4.0999999999999996</v>
       </c>
       <c r="F11">
-        <v>1657</v>
+        <v>2438</v>
       </c>
       <c r="G11" t="s">
-        <v>191</v>
+        <v>223</v>
       </c>
       <c r="H11" t="s">
-        <v>192</v>
+        <v>224</v>
       </c>
       <c r="I11" t="s">
         <v>26</v>
@@ -1652,28 +1538,28 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>208</v>
+        <v>244</v>
       </c>
       <c r="B12" t="s">
-        <v>209</v>
+        <v>245</v>
       </c>
       <c r="C12" t="s">
-        <v>210</v>
+        <v>246</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>211</v>
+        <v>247</v>
       </c>
       <c r="E12">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="F12">
-        <v>2820</v>
+        <v>925</v>
       </c>
       <c r="G12" t="s">
-        <v>212</v>
+        <v>248</v>
       </c>
       <c r="H12" t="s">
-        <v>157</v>
+        <v>249</v>
       </c>
       <c r="I12" t="s">
         <v>26</v>
@@ -1681,312 +1567,80 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>221</v>
+        <v>250</v>
       </c>
       <c r="B13" t="s">
-        <v>222</v>
+        <v>251</v>
       </c>
       <c r="C13" t="s">
-        <v>223</v>
+        <v>252</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>224</v>
+        <v>253</v>
       </c>
       <c r="E13">
-        <v>4.4000000000000004</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="F13">
-        <v>636</v>
+        <v>1970</v>
       </c>
       <c r="G13" t="s">
-        <v>225</v>
+        <v>254</v>
       </c>
       <c r="H13" t="s">
-        <v>226</v>
+        <v>255</v>
       </c>
       <c r="I13" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>232</v>
-      </c>
-      <c r="B14" t="s">
-        <v>233</v>
-      </c>
-      <c r="C14" t="s">
-        <v>234</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="E14">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="F14">
-        <v>2438</v>
-      </c>
-      <c r="G14" t="s">
-        <v>236</v>
-      </c>
-      <c r="H14" t="s">
-        <v>237</v>
-      </c>
-      <c r="I14" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>243</v>
-      </c>
-      <c r="B15" t="s">
-        <v>244</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="E15">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="F15">
-        <v>1001</v>
-      </c>
-      <c r="G15" t="s">
-        <v>245</v>
-      </c>
-      <c r="H15" t="s">
-        <v>116</v>
-      </c>
-      <c r="I15" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>260</v>
-      </c>
-      <c r="B16" t="s">
-        <v>261</v>
-      </c>
-      <c r="C16" t="s">
-        <v>262</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="E16">
-        <v>4.2</v>
-      </c>
-      <c r="F16">
-        <v>925</v>
-      </c>
-      <c r="G16" t="s">
-        <v>264</v>
-      </c>
-      <c r="H16" t="s">
-        <v>265</v>
-      </c>
-      <c r="I16" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>266</v>
-      </c>
-      <c r="B17" t="s">
-        <v>267</v>
-      </c>
-      <c r="C17" t="s">
-        <v>268</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="E17">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="F17">
-        <v>1828</v>
-      </c>
-      <c r="G17" t="s">
-        <v>270</v>
-      </c>
-      <c r="H17" t="s">
-        <v>271</v>
-      </c>
-      <c r="I17" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>272</v>
-      </c>
-      <c r="B18" t="s">
-        <v>273</v>
-      </c>
-      <c r="C18" t="s">
-        <v>274</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="E18">
-        <v>4.5</v>
-      </c>
-      <c r="F18">
-        <v>2878</v>
-      </c>
-      <c r="G18" t="s">
-        <v>275</v>
-      </c>
-      <c r="H18" t="s">
-        <v>157</v>
-      </c>
-      <c r="I18" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>276</v>
-      </c>
-      <c r="B19" t="s">
-        <v>277</v>
-      </c>
-      <c r="C19" t="s">
-        <v>278</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="E19">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="F19">
-        <v>1970</v>
-      </c>
-      <c r="G19" t="s">
-        <v>280</v>
-      </c>
-      <c r="H19" t="s">
-        <v>281</v>
-      </c>
-      <c r="I19" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>287</v>
-      </c>
-      <c r="B20" t="s">
-        <v>288</v>
-      </c>
-      <c r="C20" t="s">
-        <v>289</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="E20">
-        <v>4.2</v>
-      </c>
-      <c r="F20">
-        <v>2922</v>
-      </c>
-      <c r="G20" t="s">
-        <v>290</v>
-      </c>
-      <c r="H20" t="s">
-        <v>157</v>
-      </c>
-      <c r="I20" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>291</v>
-      </c>
-      <c r="B21" t="s">
-        <v>292</v>
-      </c>
-      <c r="C21" t="s">
-        <v>293</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E21">
-        <v>4.5</v>
-      </c>
-      <c r="F21">
-        <v>3789</v>
-      </c>
-      <c r="G21" t="s">
-        <v>294</v>
-      </c>
-      <c r="H21" t="s">
-        <v>25</v>
-      </c>
-      <c r="I21" t="s">
-        <v>26</v>
-      </c>
-    </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>304</v>
+        <v>9</v>
       </c>
       <c r="B22" t="s">
-        <v>305</v>
+        <v>10</v>
       </c>
       <c r="C22" t="s">
-        <v>306</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>211</v>
+        <v>11</v>
+      </c>
+      <c r="D22" t="s">
+        <v>12</v>
       </c>
       <c r="E22">
-        <v>3.9</v>
+        <v>4.7</v>
       </c>
       <c r="F22">
-        <v>21</v>
+        <v>11022</v>
       </c>
       <c r="G22" t="s">
-        <v>307</v>
-      </c>
-      <c r="H22" t="s">
-        <v>157</v>
+        <v>13</v>
       </c>
       <c r="I22" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="B23" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C23" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D23" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E23">
-        <v>4.7</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="F23">
-        <v>11022</v>
+        <v>5173</v>
       </c>
       <c r="G23" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="I23" t="s">
         <v>14</v>
@@ -1994,25 +1648,25 @@
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="B24" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="C24" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="D24" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="E24">
-        <v>4.4000000000000004</v>
+        <v>4.3</v>
       </c>
       <c r="F24">
-        <v>5173</v>
+        <v>5667</v>
       </c>
       <c r="G24" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="I24" t="s">
         <v>14</v>
@@ -2020,22 +1674,19 @@
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B25" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C25" t="s">
-        <v>39</v>
-      </c>
-      <c r="D25" t="s">
         <v>40</v>
       </c>
       <c r="E25">
-        <v>4.3</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="F25">
-        <v>5667</v>
+        <v>3992</v>
       </c>
       <c r="G25" t="s">
         <v>41</v>
@@ -2054,14 +1705,17 @@
       <c r="C26" t="s">
         <v>44</v>
       </c>
+      <c r="D26" t="s">
+        <v>45</v>
+      </c>
       <c r="E26">
         <v>4.4000000000000004</v>
       </c>
       <c r="F26">
-        <v>3992</v>
+        <v>3123</v>
       </c>
       <c r="G26" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I26" t="s">
         <v>14</v>
@@ -2069,25 +1723,25 @@
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B27" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C27" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D27" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E27">
-        <v>4.4000000000000004</v>
+        <v>4.3</v>
       </c>
       <c r="F27">
-        <v>3123</v>
+        <v>3659</v>
       </c>
       <c r="G27" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I27" t="s">
         <v>14</v>
@@ -2095,25 +1749,25 @@
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B28" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C28" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D28" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E28">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="F28">
-        <v>3659</v>
+        <v>221</v>
       </c>
       <c r="G28" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I28" t="s">
         <v>14</v>
@@ -2121,25 +1775,25 @@
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B29" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C29" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D29" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E29">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="F29">
-        <v>221</v>
+        <v>3326</v>
       </c>
       <c r="G29" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I29" t="s">
         <v>14</v>
@@ -2147,25 +1801,25 @@
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B30" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C30" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D30" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E30">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="F30">
-        <v>3326</v>
+        <v>2399</v>
       </c>
       <c r="G30" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I30" t="s">
         <v>14</v>
@@ -2173,25 +1827,25 @@
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B31" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C31" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D31" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E31">
-        <v>4.5</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="F31">
-        <v>2399</v>
+        <v>959</v>
       </c>
       <c r="G31" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I31" t="s">
         <v>14</v>
@@ -2199,25 +1853,25 @@
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="B32" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="C32" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="D32" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="E32">
-        <v>4.4000000000000004</v>
+        <v>4.5</v>
       </c>
       <c r="F32">
-        <v>959</v>
+        <v>4045</v>
       </c>
       <c r="G32" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="I32" t="s">
         <v>14</v>
@@ -2225,25 +1879,25 @@
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="B33" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="C33" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="D33" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="E33">
         <v>4.5</v>
       </c>
       <c r="F33">
-        <v>4045</v>
+        <v>5505</v>
       </c>
       <c r="G33" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="I33" t="s">
         <v>14</v>
@@ -2251,25 +1905,25 @@
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
+        <v>94</v>
+      </c>
+      <c r="B34" t="s">
+        <v>95</v>
+      </c>
+      <c r="C34" t="s">
+        <v>96</v>
+      </c>
+      <c r="D34" t="s">
         <v>97</v>
       </c>
-      <c r="B34" t="s">
+      <c r="E34">
+        <v>4.8</v>
+      </c>
+      <c r="F34">
+        <v>11160</v>
+      </c>
+      <c r="G34" t="s">
         <v>98</v>
-      </c>
-      <c r="C34" t="s">
-        <v>99</v>
-      </c>
-      <c r="D34" t="s">
-        <v>100</v>
-      </c>
-      <c r="E34">
-        <v>4.5</v>
-      </c>
-      <c r="F34">
-        <v>5505</v>
-      </c>
-      <c r="G34" t="s">
-        <v>101</v>
       </c>
       <c r="I34" t="s">
         <v>14</v>
@@ -2277,25 +1931,22 @@
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
+        <v>99</v>
+      </c>
+      <c r="B35" t="s">
+        <v>100</v>
+      </c>
+      <c r="C35" t="s">
+        <v>101</v>
+      </c>
+      <c r="E35">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="F35">
+        <v>2221</v>
+      </c>
+      <c r="G35" t="s">
         <v>102</v>
-      </c>
-      <c r="B35" t="s">
-        <v>103</v>
-      </c>
-      <c r="C35" t="s">
-        <v>104</v>
-      </c>
-      <c r="D35" t="s">
-        <v>105</v>
-      </c>
-      <c r="E35">
-        <v>4.8</v>
-      </c>
-      <c r="F35">
-        <v>11160</v>
-      </c>
-      <c r="G35" t="s">
-        <v>106</v>
       </c>
       <c r="I35" t="s">
         <v>14</v>
@@ -2303,22 +1954,25 @@
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B36" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C36" t="s">
-        <v>109</v>
+        <v>111</v>
+      </c>
+      <c r="D36" t="s">
+        <v>112</v>
       </c>
       <c r="E36">
         <v>4.5999999999999996</v>
       </c>
       <c r="F36">
-        <v>2221</v>
+        <v>2143</v>
       </c>
       <c r="G36" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="I36" t="s">
         <v>14</v>
@@ -2326,25 +1980,25 @@
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
+        <v>114</v>
+      </c>
+      <c r="B37" t="s">
+        <v>115</v>
+      </c>
+      <c r="C37" t="s">
+        <v>116</v>
+      </c>
+      <c r="D37" t="s">
         <v>117</v>
       </c>
-      <c r="B37" t="s">
+      <c r="E37">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="F37">
+        <v>3517</v>
+      </c>
+      <c r="G37" t="s">
         <v>118</v>
-      </c>
-      <c r="C37" t="s">
-        <v>119</v>
-      </c>
-      <c r="D37" t="s">
-        <v>120</v>
-      </c>
-      <c r="E37">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="F37">
-        <v>2143</v>
-      </c>
-      <c r="G37" t="s">
-        <v>121</v>
       </c>
       <c r="I37" t="s">
         <v>14</v>
@@ -2352,25 +2006,25 @@
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
+        <v>119</v>
+      </c>
+      <c r="B38" t="s">
+        <v>120</v>
+      </c>
+      <c r="C38" t="s">
+        <v>121</v>
+      </c>
+      <c r="D38" t="s">
         <v>122</v>
       </c>
-      <c r="B38" t="s">
+      <c r="E38">
+        <v>4.7</v>
+      </c>
+      <c r="F38">
+        <v>3317</v>
+      </c>
+      <c r="G38" t="s">
         <v>123</v>
-      </c>
-      <c r="C38" t="s">
-        <v>124</v>
-      </c>
-      <c r="D38" t="s">
-        <v>125</v>
-      </c>
-      <c r="E38">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="F38">
-        <v>3517</v>
-      </c>
-      <c r="G38" t="s">
-        <v>126</v>
       </c>
       <c r="I38" t="s">
         <v>14</v>
@@ -2378,25 +2032,25 @@
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
+        <v>124</v>
+      </c>
+      <c r="B39" t="s">
+        <v>125</v>
+      </c>
+      <c r="C39" t="s">
+        <v>126</v>
+      </c>
+      <c r="D39" t="s">
         <v>127</v>
       </c>
-      <c r="B39" t="s">
+      <c r="E39">
+        <v>4.2</v>
+      </c>
+      <c r="F39">
+        <v>1712</v>
+      </c>
+      <c r="G39" t="s">
         <v>128</v>
-      </c>
-      <c r="C39" t="s">
-        <v>129</v>
-      </c>
-      <c r="D39" t="s">
-        <v>130</v>
-      </c>
-      <c r="E39">
-        <v>4.7</v>
-      </c>
-      <c r="F39">
-        <v>3317</v>
-      </c>
-      <c r="G39" t="s">
-        <v>131</v>
       </c>
       <c r="I39" t="s">
         <v>14</v>
@@ -2404,25 +2058,25 @@
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
+        <v>129</v>
+      </c>
+      <c r="B40" t="s">
+        <v>130</v>
+      </c>
+      <c r="C40" t="s">
+        <v>131</v>
+      </c>
+      <c r="D40" t="s">
         <v>132</v>
       </c>
-      <c r="B40" t="s">
+      <c r="E40">
+        <v>4.5</v>
+      </c>
+      <c r="F40">
+        <v>5745</v>
+      </c>
+      <c r="G40" t="s">
         <v>133</v>
-      </c>
-      <c r="C40" t="s">
-        <v>134</v>
-      </c>
-      <c r="D40" t="s">
-        <v>135</v>
-      </c>
-      <c r="E40">
-        <v>4.2</v>
-      </c>
-      <c r="F40">
-        <v>1712</v>
-      </c>
-      <c r="G40" t="s">
-        <v>136</v>
       </c>
       <c r="I40" t="s">
         <v>14</v>
@@ -2430,25 +2084,25 @@
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
+        <v>134</v>
+      </c>
+      <c r="B41" t="s">
+        <v>135</v>
+      </c>
+      <c r="C41" t="s">
+        <v>136</v>
+      </c>
+      <c r="D41" t="s">
         <v>137</v>
       </c>
-      <c r="B41" t="s">
+      <c r="E41">
+        <v>4.7</v>
+      </c>
+      <c r="F41">
+        <v>487</v>
+      </c>
+      <c r="G41" t="s">
         <v>138</v>
-      </c>
-      <c r="C41" t="s">
-        <v>139</v>
-      </c>
-      <c r="D41" t="s">
-        <v>140</v>
-      </c>
-      <c r="E41">
-        <v>4.5</v>
-      </c>
-      <c r="F41">
-        <v>5745</v>
-      </c>
-      <c r="G41" t="s">
-        <v>141</v>
       </c>
       <c r="I41" t="s">
         <v>14</v>
@@ -2456,25 +2110,25 @@
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
+        <v>139</v>
+      </c>
+      <c r="B42" t="s">
+        <v>140</v>
+      </c>
+      <c r="C42" t="s">
+        <v>141</v>
+      </c>
+      <c r="D42" t="s">
         <v>142</v>
       </c>
-      <c r="B42" t="s">
+      <c r="E42">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="F42">
+        <v>1992</v>
+      </c>
+      <c r="G42" t="s">
         <v>143</v>
-      </c>
-      <c r="C42" t="s">
-        <v>144</v>
-      </c>
-      <c r="D42" t="s">
-        <v>145</v>
-      </c>
-      <c r="E42">
-        <v>4.7</v>
-      </c>
-      <c r="F42">
-        <v>487</v>
-      </c>
-      <c r="G42" t="s">
-        <v>146</v>
       </c>
       <c r="I42" t="s">
         <v>14</v>
@@ -2482,25 +2136,22 @@
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="B43" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C43" t="s">
-        <v>149</v>
-      </c>
-      <c r="D43" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E43">
-        <v>4.4000000000000004</v>
+        <v>4.5</v>
       </c>
       <c r="F43">
-        <v>1992</v>
+        <v>3696</v>
       </c>
       <c r="G43" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="I43" t="s">
         <v>14</v>
@@ -2508,22 +2159,25 @@
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="B44" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="C44" t="s">
-        <v>160</v>
+        <v>156</v>
+      </c>
+      <c r="D44" t="s">
+        <v>157</v>
       </c>
       <c r="E44">
         <v>4.5</v>
       </c>
       <c r="F44">
-        <v>3696</v>
+        <v>2681</v>
       </c>
       <c r="G44" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="I44" t="s">
         <v>14</v>
@@ -2531,25 +2185,25 @@
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
+        <v>159</v>
+      </c>
+      <c r="B45" t="s">
+        <v>160</v>
+      </c>
+      <c r="C45" t="s">
+        <v>161</v>
+      </c>
+      <c r="D45" t="s">
+        <v>97</v>
+      </c>
+      <c r="E45">
+        <v>4.8</v>
+      </c>
+      <c r="F45">
+        <v>8485</v>
+      </c>
+      <c r="G45" t="s">
         <v>162</v>
-      </c>
-      <c r="B45" t="s">
-        <v>163</v>
-      </c>
-      <c r="C45" t="s">
-        <v>164</v>
-      </c>
-      <c r="D45" t="s">
-        <v>165</v>
-      </c>
-      <c r="E45">
-        <v>4.5</v>
-      </c>
-      <c r="F45">
-        <v>2681</v>
-      </c>
-      <c r="G45" t="s">
-        <v>166</v>
       </c>
       <c r="I45" t="s">
         <v>14</v>
@@ -2557,25 +2211,25 @@
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
+        <v>163</v>
+      </c>
+      <c r="B46" t="s">
+        <v>164</v>
+      </c>
+      <c r="C46" t="s">
+        <v>165</v>
+      </c>
+      <c r="D46" t="s">
+        <v>166</v>
+      </c>
+      <c r="E46">
+        <v>4.5</v>
+      </c>
+      <c r="F46">
+        <v>1467</v>
+      </c>
+      <c r="G46" t="s">
         <v>167</v>
-      </c>
-      <c r="B46" t="s">
-        <v>168</v>
-      </c>
-      <c r="C46" t="s">
-        <v>169</v>
-      </c>
-      <c r="D46" t="s">
-        <v>105</v>
-      </c>
-      <c r="E46">
-        <v>4.8</v>
-      </c>
-      <c r="F46">
-        <v>8485</v>
-      </c>
-      <c r="G46" t="s">
-        <v>170</v>
       </c>
       <c r="I46" t="s">
         <v>14</v>
@@ -2583,25 +2237,25 @@
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="B47" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C47" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="D47" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="E47">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="F47">
-        <v>1467</v>
+        <v>88</v>
       </c>
       <c r="G47" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="I47" t="s">
         <v>14</v>
@@ -2609,25 +2263,25 @@
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="B48" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="C48" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D48" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="E48">
-        <v>4.7</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="F48">
-        <v>88</v>
+        <v>1516</v>
       </c>
       <c r="G48" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="I48" t="s">
         <v>14</v>
@@ -2635,25 +2289,25 @@
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
+        <v>190</v>
+      </c>
+      <c r="B49" t="s">
+        <v>191</v>
+      </c>
+      <c r="C49" t="s">
+        <v>192</v>
+      </c>
+      <c r="D49" t="s">
         <v>193</v>
       </c>
-      <c r="B49" t="s">
+      <c r="E49">
+        <v>4.3</v>
+      </c>
+      <c r="F49">
+        <v>820</v>
+      </c>
+      <c r="G49" t="s">
         <v>194</v>
-      </c>
-      <c r="C49" t="s">
-        <v>195</v>
-      </c>
-      <c r="D49" t="s">
-        <v>196</v>
-      </c>
-      <c r="E49">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="F49">
-        <v>1516</v>
-      </c>
-      <c r="G49" t="s">
-        <v>197</v>
       </c>
       <c r="I49" t="s">
         <v>14</v>
@@ -2661,25 +2315,25 @@
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
+        <v>195</v>
+      </c>
+      <c r="B50" t="s">
+        <v>196</v>
+      </c>
+      <c r="C50" t="s">
+        <v>197</v>
+      </c>
+      <c r="D50" t="s">
         <v>198</v>
       </c>
-      <c r="B50" t="s">
+      <c r="E50">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="F50">
+        <v>1242</v>
+      </c>
+      <c r="G50" t="s">
         <v>199</v>
-      </c>
-      <c r="C50" t="s">
-        <v>200</v>
-      </c>
-      <c r="D50" t="s">
-        <v>201</v>
-      </c>
-      <c r="E50">
-        <v>4.3</v>
-      </c>
-      <c r="F50">
-        <v>820</v>
-      </c>
-      <c r="G50" t="s">
-        <v>202</v>
       </c>
       <c r="I50" t="s">
         <v>14</v>
@@ -2687,25 +2341,25 @@
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
+        <v>200</v>
+      </c>
+      <c r="B51" t="s">
+        <v>201</v>
+      </c>
+      <c r="C51" t="s">
+        <v>202</v>
+      </c>
+      <c r="D51" t="s">
+        <v>97</v>
+      </c>
+      <c r="E51">
+        <v>4.8</v>
+      </c>
+      <c r="F51">
+        <v>7055</v>
+      </c>
+      <c r="G51" t="s">
         <v>203</v>
-      </c>
-      <c r="B51" t="s">
-        <v>204</v>
-      </c>
-      <c r="C51" t="s">
-        <v>205</v>
-      </c>
-      <c r="D51" t="s">
-        <v>206</v>
-      </c>
-      <c r="E51">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="F51">
-        <v>1242</v>
-      </c>
-      <c r="G51" t="s">
-        <v>207</v>
       </c>
       <c r="I51" t="s">
         <v>14</v>
@@ -2713,25 +2367,22 @@
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>213</v>
+        <v>204</v>
       </c>
       <c r="B52" t="s">
-        <v>214</v>
+        <v>205</v>
       </c>
       <c r="C52" t="s">
-        <v>215</v>
-      </c>
-      <c r="D52" t="s">
-        <v>105</v>
+        <v>206</v>
       </c>
       <c r="E52">
-        <v>4.8</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="F52">
-        <v>7055</v>
+        <v>1046</v>
       </c>
       <c r="G52" t="s">
-        <v>216</v>
+        <v>207</v>
       </c>
       <c r="I52" t="s">
         <v>14</v>
@@ -2739,22 +2390,25 @@
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
+        <v>214</v>
+      </c>
+      <c r="B53" t="s">
+        <v>215</v>
+      </c>
+      <c r="C53" t="s">
+        <v>216</v>
+      </c>
+      <c r="D53" t="s">
         <v>217</v>
-      </c>
-      <c r="B53" t="s">
-        <v>218</v>
-      </c>
-      <c r="C53" t="s">
-        <v>219</v>
       </c>
       <c r="E53">
         <v>4.4000000000000004</v>
       </c>
       <c r="F53">
-        <v>1046</v>
+        <v>1619</v>
       </c>
       <c r="G53" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="I53" t="s">
         <v>14</v>
@@ -2762,25 +2416,25 @@
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
+        <v>225</v>
+      </c>
+      <c r="B54" t="s">
+        <v>226</v>
+      </c>
+      <c r="C54" t="s">
         <v>227</v>
       </c>
-      <c r="B54" t="s">
+      <c r="D54" t="s">
         <v>228</v>
-      </c>
-      <c r="C54" t="s">
-        <v>229</v>
-      </c>
-      <c r="D54" t="s">
-        <v>230</v>
       </c>
       <c r="E54">
         <v>4.4000000000000004</v>
       </c>
       <c r="F54">
-        <v>1619</v>
+        <v>1392</v>
       </c>
       <c r="G54" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="I54" t="s">
         <v>14</v>
@@ -2788,25 +2442,25 @@
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="B55" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="C55" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="D55" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="E55">
-        <v>4.4000000000000004</v>
+        <v>4.7</v>
       </c>
       <c r="F55">
-        <v>1392</v>
+        <v>12011</v>
       </c>
       <c r="G55" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="I55" t="s">
         <v>14</v>
@@ -2814,25 +2468,25 @@
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>246</v>
+        <v>235</v>
       </c>
       <c r="B56" t="s">
-        <v>247</v>
+        <v>236</v>
       </c>
       <c r="C56" t="s">
-        <v>248</v>
+        <v>237</v>
       </c>
       <c r="D56" t="s">
-        <v>249</v>
+        <v>233</v>
       </c>
       <c r="E56">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="F56">
-        <v>12011</v>
+        <v>16811</v>
       </c>
       <c r="G56" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="I56" t="s">
         <v>14</v>
@@ -2840,25 +2494,25 @@
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="B57" t="s">
-        <v>252</v>
+        <v>240</v>
       </c>
       <c r="C57" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="D57" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="E57">
-        <v>4.8</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="F57">
-        <v>16811</v>
+        <v>1888</v>
       </c>
       <c r="G57" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="I57" t="s">
         <v>14</v>
@@ -2866,25 +2520,25 @@
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B58" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C58" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D58" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E58">
-        <v>4.4000000000000004</v>
+        <v>4.3</v>
       </c>
       <c r="F58">
-        <v>1888</v>
+        <v>2252</v>
       </c>
       <c r="G58" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="I58" t="s">
         <v>14</v>
@@ -2892,25 +2546,25 @@
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>282</v>
+        <v>261</v>
       </c>
       <c r="B59" t="s">
-        <v>283</v>
+        <v>262</v>
       </c>
       <c r="C59" t="s">
-        <v>284</v>
+        <v>263</v>
       </c>
       <c r="D59" t="s">
-        <v>285</v>
+        <v>264</v>
       </c>
       <c r="E59">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="F59">
-        <v>2252</v>
+        <v>1335</v>
       </c>
       <c r="G59" t="s">
-        <v>286</v>
+        <v>265</v>
       </c>
       <c r="I59" t="s">
         <v>14</v>
@@ -2918,59 +2572,33 @@
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>295</v>
+        <v>266</v>
       </c>
       <c r="B60" t="s">
-        <v>296</v>
+        <v>267</v>
       </c>
       <c r="C60" t="s">
-        <v>297</v>
+        <v>268</v>
       </c>
       <c r="D60" t="s">
-        <v>298</v>
+        <v>228</v>
       </c>
       <c r="E60">
-        <v>4.5</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="F60">
-        <v>1335</v>
+        <v>1107</v>
       </c>
       <c r="G60" t="s">
-        <v>299</v>
+        <v>269</v>
       </c>
       <c r="I60" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A61" t="s">
-        <v>300</v>
-      </c>
-      <c r="B61" t="s">
-        <v>301</v>
-      </c>
-      <c r="C61" t="s">
-        <v>302</v>
-      </c>
-      <c r="D61" t="s">
-        <v>241</v>
-      </c>
-      <c r="E61">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="F61">
-        <v>1107</v>
-      </c>
-      <c r="G61" t="s">
-        <v>303</v>
-      </c>
-      <c r="I61" t="s">
-        <v>14</v>
-      </c>
-    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I61">
-    <sortCondition ref="I2:I61"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I60">
+    <sortCondition ref="I2:I60"/>
   </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/restaurant_crawler/restaurant_data_台北_牛排_20250910_192841_with_emails.xlsx
+++ b/restaurant_crawler/restaurant_data_台北_牛排_20250910_192841_with_emails.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\slow3\OneDrive\桌面\GitHubProjects\BYOB\restaurant_crawler\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89D8AC7B-BAAE-46C0-A568-A5554E2AB1C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32206034-F938-45BD-9C2E-59940CEF9B28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="245">
   <si>
     <t>name</t>
   </si>
@@ -121,48 +121,6 @@
     <t>customerservice@regenthotelsgroup.com</t>
   </si>
   <si>
-    <t>莫爾頓牛排館</t>
-  </si>
-  <si>
-    <t>110台灣台北市信義區忠孝東路五段68號45F</t>
-  </si>
-  <si>
-    <t>02 2723 7000</t>
-  </si>
-  <si>
-    <t>https://www.mortons.com/location/mortons-the-steakhouse-taipei/</t>
-  </si>
-  <si>
-    <t>ChIJPbbLlLurQjQRumJSj8aVbmk</t>
-  </si>
-  <si>
-    <t>樂邦</t>
-  </si>
-  <si>
-    <t>106台灣台北市大安區大安路一段183號</t>
-  </si>
-  <si>
-    <t>02 2700 7770</t>
-  </si>
-  <si>
-    <t>ChIJ1aexh9GrQjQRBdl35-SffoQ</t>
-  </si>
-  <si>
-    <t>(台北國賓大飯店)A CUT牛排館</t>
-  </si>
-  <si>
-    <t>104105台灣台北市中山區遼寧街177號2樓</t>
-  </si>
-  <si>
-    <t>02 2571 0389</t>
-  </si>
-  <si>
-    <t>https://www.ambassador-hotels.com/tc/taipei/dining/a-cut-steakhouse#story</t>
-  </si>
-  <si>
-    <t>ChIJ-eTvMWipQjQRIzqciZ5uD5E</t>
-  </si>
-  <si>
     <t>雅室牛排 仁愛圓環店</t>
   </si>
   <si>
@@ -178,21 +136,6 @@
     <t>ChIJGzqUC8-rQjQR8d5fRKpaNQo</t>
   </si>
   <si>
-    <t>AJ grill</t>
-  </si>
-  <si>
-    <t>106063台灣台北市大安區安和路一段135巷10號</t>
-  </si>
-  <si>
-    <t>02 2709 0293</t>
-  </si>
-  <si>
-    <t>https://www.instagram.com/ajgrill/</t>
-  </si>
-  <si>
-    <t>ChIJPQFnJS6rQjQRJ8N8ts6FuJ0</t>
-  </si>
-  <si>
     <t>勞瑞斯牛肋排餐廳</t>
   </si>
   <si>
@@ -256,21 +199,6 @@
     <t>injoytrucker@gmail.com</t>
   </si>
   <si>
-    <t>水牛城美式炭烤牛排（古亭）</t>
-  </si>
-  <si>
-    <t>100台灣台北市中正區杭州南路二段94號</t>
-  </si>
-  <si>
-    <t>02 2351 7633</t>
-  </si>
-  <si>
-    <t>https://buffalo-tw.com/</t>
-  </si>
-  <si>
-    <t>ChIJkT9RupupQjQROzXoveyqnmU</t>
-  </si>
-  <si>
     <t>茱莉金牛排餐酒館</t>
   </si>
   <si>
@@ -319,18 +247,6 @@
     <t>ChIJVz_H32ipQjQRDDbDTPoI01Q</t>
   </si>
   <si>
-    <t>瀧厚炙燒熟成牛排 台北.信義ATT店</t>
-  </si>
-  <si>
-    <t>110台灣台北市信义区松寿路12號ATT 4 FUN5樓</t>
-  </si>
-  <si>
-    <t>02 7734 2008</t>
-  </si>
-  <si>
-    <t>ChIJieKHJvurQjQRV0sWxBYJhfI</t>
-  </si>
-  <si>
     <t>教父牛排 Danny's Steak House</t>
   </si>
   <si>
@@ -349,21 +265,6 @@
     <t>service@danhouse.com.tw</t>
   </si>
   <si>
-    <t>地中海牛排館</t>
-  </si>
-  <si>
-    <t>104台灣台北市中山區林森北路646號1樓</t>
-  </si>
-  <si>
-    <t>02 2585 3258#804</t>
-  </si>
-  <si>
-    <t>https://www.rivierataipei.com/zh-hant/dining/the-mediterranean-steak-house/</t>
-  </si>
-  <si>
-    <t>ChIJ4TtsHVCpQjQRPZMEBFzvSJs</t>
-  </si>
-  <si>
     <t>茹絲葵美式牛排（台北民生店）</t>
   </si>
   <si>
@@ -830,6 +731,32 @@
   </si>
   <si>
     <t>ChIJt7JDM4KrQjQRjbeuPqbQQ8A</t>
+  </si>
+  <si>
+    <t>m</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>info@swtpe.com</t>
+  </si>
+  <si>
+    <t>x</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>service@grandvictoria.com.tw</t>
+  </si>
+  <si>
+    <t>fo@taipeigarden.com.tw</t>
+  </si>
+  <si>
+    <t>stonegrill@outlook.com</t>
+  </si>
+  <si>
+    <t>service@wangsteak.com.tw</t>
+  </si>
+  <si>
+    <t>taipei.ms@ruthschris.com.tw</t>
   </si>
 </sst>
 </file>
@@ -1208,7 +1135,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I60"/>
+  <dimension ref="A1:K47"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="40.375" customWidth="1"/>
@@ -1306,16 +1233,16 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="B4" t="s">
-        <v>73</v>
+        <v>54</v>
       </c>
       <c r="C4" t="s">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>75</v>
+        <v>56</v>
       </c>
       <c r="E4">
         <v>4.5999999999999996</v>
@@ -1324,10 +1251,10 @@
         <v>6738</v>
       </c>
       <c r="G4" t="s">
-        <v>76</v>
+        <v>57</v>
       </c>
       <c r="H4" t="s">
-        <v>77</v>
+        <v>58</v>
       </c>
       <c r="I4" t="s">
         <v>26</v>
@@ -1335,16 +1262,16 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>83</v>
+        <v>59</v>
       </c>
       <c r="B5" t="s">
-        <v>84</v>
+        <v>60</v>
       </c>
       <c r="C5" t="s">
-        <v>85</v>
+        <v>61</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>86</v>
+        <v>62</v>
       </c>
       <c r="E5">
         <v>4.5</v>
@@ -1353,10 +1280,10 @@
         <v>1771</v>
       </c>
       <c r="G5" t="s">
-        <v>87</v>
+        <v>63</v>
       </c>
       <c r="H5" t="s">
-        <v>88</v>
+        <v>64</v>
       </c>
       <c r="I5" t="s">
         <v>26</v>
@@ -1364,16 +1291,16 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>103</v>
+        <v>75</v>
       </c>
       <c r="B6" t="s">
-        <v>104</v>
+        <v>76</v>
       </c>
       <c r="C6" t="s">
-        <v>105</v>
+        <v>77</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>106</v>
+        <v>78</v>
       </c>
       <c r="E6">
         <v>4.2</v>
@@ -1382,10 +1309,10 @@
         <v>4469</v>
       </c>
       <c r="G6" t="s">
-        <v>107</v>
+        <v>79</v>
       </c>
       <c r="H6" t="s">
-        <v>108</v>
+        <v>80</v>
       </c>
       <c r="I6" t="s">
         <v>26</v>
@@ -1393,16 +1320,16 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>144</v>
+        <v>111</v>
       </c>
       <c r="B7" t="s">
-        <v>145</v>
+        <v>112</v>
       </c>
       <c r="C7" t="s">
-        <v>146</v>
+        <v>113</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>147</v>
+        <v>114</v>
       </c>
       <c r="E7">
         <v>4.3</v>
@@ -1411,10 +1338,10 @@
         <v>2018</v>
       </c>
       <c r="G7" t="s">
-        <v>148</v>
+        <v>115</v>
       </c>
       <c r="H7" t="s">
-        <v>149</v>
+        <v>116</v>
       </c>
       <c r="I7" t="s">
         <v>26</v>
@@ -1422,16 +1349,16 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>168</v>
+        <v>135</v>
       </c>
       <c r="B8" t="s">
-        <v>169</v>
+        <v>136</v>
       </c>
       <c r="C8" t="s">
-        <v>170</v>
+        <v>137</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>171</v>
+        <v>138</v>
       </c>
       <c r="E8">
         <v>4.5</v>
@@ -1440,10 +1367,10 @@
         <v>4412</v>
       </c>
       <c r="G8" t="s">
-        <v>172</v>
+        <v>139</v>
       </c>
       <c r="H8" t="s">
-        <v>173</v>
+        <v>140</v>
       </c>
       <c r="I8" t="s">
         <v>26</v>
@@ -1451,16 +1378,16 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>179</v>
+        <v>146</v>
       </c>
       <c r="B9" t="s">
-        <v>180</v>
+        <v>147</v>
       </c>
       <c r="C9" t="s">
-        <v>181</v>
+        <v>148</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>182</v>
+        <v>149</v>
       </c>
       <c r="E9">
         <v>4.0999999999999996</v>
@@ -1469,10 +1396,10 @@
         <v>1657</v>
       </c>
       <c r="G9" t="s">
-        <v>183</v>
+        <v>150</v>
       </c>
       <c r="H9" t="s">
-        <v>184</v>
+        <v>151</v>
       </c>
       <c r="I9" t="s">
         <v>26</v>
@@ -1480,16 +1407,16 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>208</v>
+        <v>175</v>
       </c>
       <c r="B10" t="s">
-        <v>209</v>
+        <v>176</v>
       </c>
       <c r="C10" t="s">
-        <v>210</v>
+        <v>177</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>211</v>
+        <v>178</v>
       </c>
       <c r="E10">
         <v>4.4000000000000004</v>
@@ -1498,10 +1425,10 @@
         <v>636</v>
       </c>
       <c r="G10" t="s">
-        <v>212</v>
+        <v>179</v>
       </c>
       <c r="H10" t="s">
-        <v>213</v>
+        <v>180</v>
       </c>
       <c r="I10" t="s">
         <v>26</v>
@@ -1509,16 +1436,16 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>219</v>
+        <v>186</v>
       </c>
       <c r="B11" t="s">
-        <v>220</v>
+        <v>187</v>
       </c>
       <c r="C11" t="s">
-        <v>221</v>
+        <v>188</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>222</v>
+        <v>189</v>
       </c>
       <c r="E11">
         <v>4.0999999999999996</v>
@@ -1527,10 +1454,10 @@
         <v>2438</v>
       </c>
       <c r="G11" t="s">
-        <v>223</v>
+        <v>190</v>
       </c>
       <c r="H11" t="s">
-        <v>224</v>
+        <v>191</v>
       </c>
       <c r="I11" t="s">
         <v>26</v>
@@ -1538,16 +1465,16 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>244</v>
+        <v>211</v>
       </c>
       <c r="B12" t="s">
-        <v>245</v>
+        <v>212</v>
       </c>
       <c r="C12" t="s">
-        <v>246</v>
+        <v>213</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>247</v>
+        <v>214</v>
       </c>
       <c r="E12">
         <v>4.2</v>
@@ -1556,10 +1483,10 @@
         <v>925</v>
       </c>
       <c r="G12" t="s">
-        <v>248</v>
+        <v>215</v>
       </c>
       <c r="H12" t="s">
-        <v>249</v>
+        <v>216</v>
       </c>
       <c r="I12" t="s">
         <v>26</v>
@@ -1567,16 +1494,16 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>250</v>
+        <v>217</v>
       </c>
       <c r="B13" t="s">
-        <v>251</v>
+        <v>218</v>
       </c>
       <c r="C13" t="s">
-        <v>252</v>
+        <v>219</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>253</v>
+        <v>220</v>
       </c>
       <c r="E13">
         <v>4.0999999999999996</v>
@@ -1585,16 +1512,190 @@
         <v>1970</v>
       </c>
       <c r="G13" t="s">
-        <v>254</v>
+        <v>221</v>
       </c>
       <c r="H13" t="s">
-        <v>255</v>
+        <v>222</v>
       </c>
       <c r="I13" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14" t="s">
+        <v>44</v>
+      </c>
+      <c r="C14" t="s">
+        <v>45</v>
+      </c>
+      <c r="D14" t="s">
+        <v>46</v>
+      </c>
+      <c r="E14">
+        <v>4.5</v>
+      </c>
+      <c r="F14">
+        <v>2399</v>
+      </c>
+      <c r="G14" t="s">
+        <v>47</v>
+      </c>
+      <c r="H14" t="s">
+        <v>240</v>
+      </c>
+      <c r="I14" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" t="s">
+        <v>17</v>
+      </c>
+      <c r="D15" t="s">
+        <v>18</v>
+      </c>
+      <c r="E15">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="F15">
+        <v>5173</v>
+      </c>
+      <c r="G15" t="s">
+        <v>19</v>
+      </c>
+      <c r="H15" t="s">
+        <v>238</v>
+      </c>
+      <c r="I15" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>48</v>
+      </c>
+      <c r="B16" t="s">
+        <v>49</v>
+      </c>
+      <c r="C16" t="s">
+        <v>50</v>
+      </c>
+      <c r="D16" t="s">
+        <v>51</v>
+      </c>
+      <c r="E16">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="F16">
+        <v>959</v>
+      </c>
+      <c r="G16" t="s">
+        <v>52</v>
+      </c>
+      <c r="H16" t="s">
+        <v>241</v>
+      </c>
+      <c r="I16" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>65</v>
+      </c>
+      <c r="B17" t="s">
+        <v>66</v>
+      </c>
+      <c r="C17" t="s">
+        <v>67</v>
+      </c>
+      <c r="D17" t="s">
+        <v>68</v>
+      </c>
+      <c r="E17">
+        <v>4.5</v>
+      </c>
+      <c r="F17">
+        <v>5505</v>
+      </c>
+      <c r="G17" t="s">
+        <v>69</v>
+      </c>
+      <c r="H17" t="s">
+        <v>242</v>
+      </c>
+      <c r="I17" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>70</v>
+      </c>
+      <c r="B18" t="s">
+        <v>71</v>
+      </c>
+      <c r="C18" t="s">
+        <v>72</v>
+      </c>
+      <c r="D18" t="s">
+        <v>73</v>
+      </c>
+      <c r="E18">
+        <v>4.8</v>
+      </c>
+      <c r="F18">
+        <v>11160</v>
+      </c>
+      <c r="G18" t="s">
+        <v>74</v>
+      </c>
+      <c r="H18" t="s">
+        <v>243</v>
+      </c>
+      <c r="I18" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>81</v>
+      </c>
+      <c r="B19" t="s">
+        <v>82</v>
+      </c>
+      <c r="C19" t="s">
+        <v>83</v>
+      </c>
+      <c r="D19" t="s">
+        <v>84</v>
+      </c>
+      <c r="E19">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="F19">
+        <v>3517</v>
+      </c>
+      <c r="G19" t="s">
+        <v>85</v>
+      </c>
+      <c r="H19" t="s">
+        <v>244</v>
+      </c>
+      <c r="I19" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>9</v>
       </c>
@@ -1619,259 +1720,268 @@
       <c r="I22" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J22" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="B23" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="C23" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="D23" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="E23">
-        <v>4.4000000000000004</v>
+        <v>4.3</v>
       </c>
       <c r="F23">
-        <v>5173</v>
+        <v>3659</v>
       </c>
       <c r="G23" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="I23" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="B24" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="C24" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="D24" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="E24">
         <v>4.3</v>
       </c>
       <c r="F24">
-        <v>5667</v>
+        <v>3326</v>
       </c>
       <c r="G24" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I24" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J24" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>38</v>
+        <v>86</v>
       </c>
       <c r="B25" t="s">
-        <v>39</v>
+        <v>87</v>
       </c>
       <c r="C25" t="s">
-        <v>40</v>
+        <v>88</v>
+      </c>
+      <c r="D25" t="s">
+        <v>89</v>
       </c>
       <c r="E25">
-        <v>4.4000000000000004</v>
+        <v>4.7</v>
       </c>
       <c r="F25">
-        <v>3992</v>
+        <v>3317</v>
       </c>
       <c r="G25" t="s">
-        <v>41</v>
+        <v>90</v>
       </c>
       <c r="I25" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="K25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>42</v>
+        <v>91</v>
       </c>
       <c r="B26" t="s">
-        <v>43</v>
+        <v>92</v>
       </c>
       <c r="C26" t="s">
-        <v>44</v>
+        <v>93</v>
       </c>
       <c r="D26" t="s">
-        <v>45</v>
+        <v>94</v>
       </c>
       <c r="E26">
-        <v>4.4000000000000004</v>
+        <v>4.2</v>
       </c>
       <c r="F26">
-        <v>3123</v>
+        <v>1712</v>
       </c>
       <c r="G26" t="s">
-        <v>46</v>
+        <v>95</v>
       </c>
       <c r="I26" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>47</v>
+        <v>96</v>
       </c>
       <c r="B27" t="s">
-        <v>48</v>
+        <v>97</v>
       </c>
       <c r="C27" t="s">
-        <v>49</v>
+        <v>98</v>
       </c>
       <c r="D27" t="s">
-        <v>50</v>
+        <v>99</v>
       </c>
       <c r="E27">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="F27">
-        <v>3659</v>
+        <v>5745</v>
       </c>
       <c r="G27" t="s">
-        <v>51</v>
+        <v>100</v>
       </c>
       <c r="I27" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>52</v>
+        <v>101</v>
       </c>
       <c r="B28" t="s">
-        <v>53</v>
+        <v>102</v>
       </c>
       <c r="C28" t="s">
-        <v>54</v>
+        <v>103</v>
       </c>
       <c r="D28" t="s">
-        <v>55</v>
+        <v>104</v>
       </c>
       <c r="E28">
         <v>4.7</v>
       </c>
       <c r="F28">
-        <v>221</v>
+        <v>487</v>
       </c>
       <c r="G28" t="s">
-        <v>56</v>
+        <v>105</v>
       </c>
       <c r="I28" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>57</v>
+        <v>106</v>
       </c>
       <c r="B29" t="s">
-        <v>58</v>
+        <v>107</v>
       </c>
       <c r="C29" t="s">
-        <v>59</v>
+        <v>108</v>
       </c>
       <c r="D29" t="s">
-        <v>60</v>
+        <v>109</v>
       </c>
       <c r="E29">
-        <v>4.3</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="F29">
-        <v>3326</v>
+        <v>1992</v>
       </c>
       <c r="G29" t="s">
-        <v>61</v>
+        <v>110</v>
       </c>
       <c r="I29" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>62</v>
+        <v>117</v>
       </c>
       <c r="B30" t="s">
-        <v>63</v>
+        <v>118</v>
       </c>
       <c r="C30" t="s">
-        <v>64</v>
-      </c>
-      <c r="D30" t="s">
-        <v>65</v>
+        <v>119</v>
       </c>
       <c r="E30">
         <v>4.5</v>
       </c>
       <c r="F30">
-        <v>2399</v>
+        <v>3696</v>
       </c>
       <c r="G30" t="s">
-        <v>66</v>
+        <v>120</v>
       </c>
       <c r="I30" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>67</v>
+        <v>121</v>
       </c>
       <c r="B31" t="s">
-        <v>68</v>
+        <v>122</v>
       </c>
       <c r="C31" t="s">
-        <v>69</v>
+        <v>123</v>
       </c>
       <c r="D31" t="s">
-        <v>70</v>
+        <v>124</v>
       </c>
       <c r="E31">
-        <v>4.4000000000000004</v>
+        <v>4.5</v>
       </c>
       <c r="F31">
-        <v>959</v>
+        <v>2681</v>
       </c>
       <c r="G31" t="s">
-        <v>71</v>
+        <v>125</v>
       </c>
       <c r="I31" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>78</v>
+        <v>126</v>
       </c>
       <c r="B32" t="s">
-        <v>79</v>
+        <v>127</v>
       </c>
       <c r="C32" t="s">
-        <v>80</v>
+        <v>128</v>
       </c>
       <c r="D32" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="E32">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="F32">
-        <v>4045</v>
+        <v>8485</v>
       </c>
       <c r="G32" t="s">
-        <v>82</v>
+        <v>129</v>
       </c>
       <c r="I32" t="s">
         <v>14</v>
@@ -1879,25 +1989,25 @@
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>89</v>
+        <v>130</v>
       </c>
       <c r="B33" t="s">
-        <v>90</v>
+        <v>131</v>
       </c>
       <c r="C33" t="s">
-        <v>91</v>
+        <v>132</v>
       </c>
       <c r="D33" t="s">
-        <v>92</v>
+        <v>133</v>
       </c>
       <c r="E33">
         <v>4.5</v>
       </c>
       <c r="F33">
-        <v>5505</v>
+        <v>1467</v>
       </c>
       <c r="G33" t="s">
-        <v>93</v>
+        <v>134</v>
       </c>
       <c r="I33" t="s">
         <v>14</v>
@@ -1905,25 +2015,25 @@
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>94</v>
+        <v>141</v>
       </c>
       <c r="B34" t="s">
-        <v>95</v>
+        <v>142</v>
       </c>
       <c r="C34" t="s">
-        <v>96</v>
+        <v>143</v>
       </c>
       <c r="D34" t="s">
-        <v>97</v>
+        <v>144</v>
       </c>
       <c r="E34">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="F34">
-        <v>11160</v>
+        <v>88</v>
       </c>
       <c r="G34" t="s">
-        <v>98</v>
+        <v>145</v>
       </c>
       <c r="I34" t="s">
         <v>14</v>
@@ -1931,22 +2041,25 @@
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>99</v>
+        <v>152</v>
       </c>
       <c r="B35" t="s">
-        <v>100</v>
+        <v>153</v>
       </c>
       <c r="C35" t="s">
-        <v>101</v>
+        <v>154</v>
+      </c>
+      <c r="D35" t="s">
+        <v>155</v>
       </c>
       <c r="E35">
-        <v>4.5999999999999996</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="F35">
-        <v>2221</v>
+        <v>1516</v>
       </c>
       <c r="G35" t="s">
-        <v>102</v>
+        <v>156</v>
       </c>
       <c r="I35" t="s">
         <v>14</v>
@@ -1954,25 +2067,25 @@
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>109</v>
+        <v>157</v>
       </c>
       <c r="B36" t="s">
-        <v>110</v>
+        <v>158</v>
       </c>
       <c r="C36" t="s">
-        <v>111</v>
+        <v>159</v>
       </c>
       <c r="D36" t="s">
-        <v>112</v>
+        <v>160</v>
       </c>
       <c r="E36">
-        <v>4.5999999999999996</v>
+        <v>4.3</v>
       </c>
       <c r="F36">
-        <v>2143</v>
+        <v>820</v>
       </c>
       <c r="G36" t="s">
-        <v>113</v>
+        <v>161</v>
       </c>
       <c r="I36" t="s">
         <v>14</v>
@@ -1980,25 +2093,25 @@
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>114</v>
+        <v>162</v>
       </c>
       <c r="B37" t="s">
-        <v>115</v>
+        <v>163</v>
       </c>
       <c r="C37" t="s">
-        <v>116</v>
+        <v>164</v>
       </c>
       <c r="D37" t="s">
-        <v>117</v>
+        <v>165</v>
       </c>
       <c r="E37">
         <v>4.4000000000000004</v>
       </c>
       <c r="F37">
-        <v>3517</v>
+        <v>1242</v>
       </c>
       <c r="G37" t="s">
-        <v>118</v>
+        <v>166</v>
       </c>
       <c r="I37" t="s">
         <v>14</v>
@@ -2006,25 +2119,25 @@
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>119</v>
+        <v>167</v>
       </c>
       <c r="B38" t="s">
-        <v>120</v>
+        <v>168</v>
       </c>
       <c r="C38" t="s">
-        <v>121</v>
+        <v>169</v>
       </c>
       <c r="D38" t="s">
-        <v>122</v>
+        <v>73</v>
       </c>
       <c r="E38">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="F38">
-        <v>3317</v>
+        <v>7055</v>
       </c>
       <c r="G38" t="s">
-        <v>123</v>
+        <v>170</v>
       </c>
       <c r="I38" t="s">
         <v>14</v>
@@ -2032,25 +2145,22 @@
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>124</v>
+        <v>171</v>
       </c>
       <c r="B39" t="s">
-        <v>125</v>
+        <v>172</v>
       </c>
       <c r="C39" t="s">
-        <v>126</v>
-      </c>
-      <c r="D39" t="s">
-        <v>127</v>
+        <v>173</v>
       </c>
       <c r="E39">
-        <v>4.2</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="F39">
-        <v>1712</v>
+        <v>1046</v>
       </c>
       <c r="G39" t="s">
-        <v>128</v>
+        <v>174</v>
       </c>
       <c r="I39" t="s">
         <v>14</v>
@@ -2058,25 +2168,25 @@
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>129</v>
+        <v>181</v>
       </c>
       <c r="B40" t="s">
-        <v>130</v>
+        <v>182</v>
       </c>
       <c r="C40" t="s">
-        <v>131</v>
+        <v>183</v>
       </c>
       <c r="D40" t="s">
-        <v>132</v>
+        <v>184</v>
       </c>
       <c r="E40">
-        <v>4.5</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="F40">
-        <v>5745</v>
+        <v>1619</v>
       </c>
       <c r="G40" t="s">
-        <v>133</v>
+        <v>185</v>
       </c>
       <c r="I40" t="s">
         <v>14</v>
@@ -2084,25 +2194,25 @@
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>134</v>
+        <v>192</v>
       </c>
       <c r="B41" t="s">
-        <v>135</v>
+        <v>193</v>
       </c>
       <c r="C41" t="s">
-        <v>136</v>
+        <v>194</v>
       </c>
       <c r="D41" t="s">
-        <v>137</v>
+        <v>195</v>
       </c>
       <c r="E41">
-        <v>4.7</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="F41">
-        <v>487</v>
+        <v>1392</v>
       </c>
       <c r="G41" t="s">
-        <v>138</v>
+        <v>196</v>
       </c>
       <c r="I41" t="s">
         <v>14</v>
@@ -2110,25 +2220,25 @@
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>139</v>
+        <v>197</v>
       </c>
       <c r="B42" t="s">
-        <v>140</v>
+        <v>198</v>
       </c>
       <c r="C42" t="s">
-        <v>141</v>
+        <v>199</v>
       </c>
       <c r="D42" t="s">
-        <v>142</v>
+        <v>200</v>
       </c>
       <c r="E42">
-        <v>4.4000000000000004</v>
+        <v>4.7</v>
       </c>
       <c r="F42">
-        <v>1992</v>
+        <v>12011</v>
       </c>
       <c r="G42" t="s">
-        <v>143</v>
+        <v>201</v>
       </c>
       <c r="I42" t="s">
         <v>14</v>
@@ -2136,22 +2246,25 @@
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>150</v>
+        <v>202</v>
       </c>
       <c r="B43" t="s">
-        <v>151</v>
+        <v>203</v>
       </c>
       <c r="C43" t="s">
-        <v>152</v>
+        <v>204</v>
+      </c>
+      <c r="D43" t="s">
+        <v>200</v>
       </c>
       <c r="E43">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="F43">
-        <v>3696</v>
+        <v>16811</v>
       </c>
       <c r="G43" t="s">
-        <v>153</v>
+        <v>205</v>
       </c>
       <c r="I43" t="s">
         <v>14</v>
@@ -2159,25 +2272,25 @@
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>154</v>
+        <v>206</v>
       </c>
       <c r="B44" t="s">
-        <v>155</v>
+        <v>207</v>
       </c>
       <c r="C44" t="s">
-        <v>156</v>
+        <v>208</v>
       </c>
       <c r="D44" t="s">
-        <v>157</v>
+        <v>209</v>
       </c>
       <c r="E44">
-        <v>4.5</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="F44">
-        <v>2681</v>
+        <v>1888</v>
       </c>
       <c r="G44" t="s">
-        <v>158</v>
+        <v>210</v>
       </c>
       <c r="I44" t="s">
         <v>14</v>
@@ -2185,25 +2298,25 @@
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>159</v>
+        <v>223</v>
       </c>
       <c r="B45" t="s">
-        <v>160</v>
+        <v>224</v>
       </c>
       <c r="C45" t="s">
-        <v>161</v>
+        <v>225</v>
       </c>
       <c r="D45" t="s">
-        <v>97</v>
+        <v>226</v>
       </c>
       <c r="E45">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="F45">
-        <v>8485</v>
+        <v>2252</v>
       </c>
       <c r="G45" t="s">
-        <v>162</v>
+        <v>227</v>
       </c>
       <c r="I45" t="s">
         <v>14</v>
@@ -2211,25 +2324,25 @@
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>163</v>
+        <v>228</v>
       </c>
       <c r="B46" t="s">
-        <v>164</v>
+        <v>229</v>
       </c>
       <c r="C46" t="s">
-        <v>165</v>
+        <v>230</v>
       </c>
       <c r="D46" t="s">
-        <v>166</v>
+        <v>231</v>
       </c>
       <c r="E46">
         <v>4.5</v>
       </c>
       <c r="F46">
-        <v>1467</v>
+        <v>1335</v>
       </c>
       <c r="G46" t="s">
-        <v>167</v>
+        <v>232</v>
       </c>
       <c r="I46" t="s">
         <v>14</v>
@@ -2237,368 +2350,33 @@
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>174</v>
+        <v>233</v>
       </c>
       <c r="B47" t="s">
-        <v>175</v>
+        <v>234</v>
       </c>
       <c r="C47" t="s">
-        <v>176</v>
+        <v>235</v>
       </c>
       <c r="D47" t="s">
-        <v>177</v>
+        <v>195</v>
       </c>
       <c r="E47">
-        <v>4.7</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="F47">
-        <v>88</v>
+        <v>1107</v>
       </c>
       <c r="G47" t="s">
-        <v>178</v>
+        <v>236</v>
       </c>
       <c r="I47" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A48" t="s">
-        <v>185</v>
-      </c>
-      <c r="B48" t="s">
-        <v>186</v>
-      </c>
-      <c r="C48" t="s">
-        <v>187</v>
-      </c>
-      <c r="D48" t="s">
-        <v>188</v>
-      </c>
-      <c r="E48">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="F48">
-        <v>1516</v>
-      </c>
-      <c r="G48" t="s">
-        <v>189</v>
-      </c>
-      <c r="I48" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A49" t="s">
-        <v>190</v>
-      </c>
-      <c r="B49" t="s">
-        <v>191</v>
-      </c>
-      <c r="C49" t="s">
-        <v>192</v>
-      </c>
-      <c r="D49" t="s">
-        <v>193</v>
-      </c>
-      <c r="E49">
-        <v>4.3</v>
-      </c>
-      <c r="F49">
-        <v>820</v>
-      </c>
-      <c r="G49" t="s">
-        <v>194</v>
-      </c>
-      <c r="I49" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
-        <v>195</v>
-      </c>
-      <c r="B50" t="s">
-        <v>196</v>
-      </c>
-      <c r="C50" t="s">
-        <v>197</v>
-      </c>
-      <c r="D50" t="s">
-        <v>198</v>
-      </c>
-      <c r="E50">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="F50">
-        <v>1242</v>
-      </c>
-      <c r="G50" t="s">
-        <v>199</v>
-      </c>
-      <c r="I50" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A51" t="s">
-        <v>200</v>
-      </c>
-      <c r="B51" t="s">
-        <v>201</v>
-      </c>
-      <c r="C51" t="s">
-        <v>202</v>
-      </c>
-      <c r="D51" t="s">
-        <v>97</v>
-      </c>
-      <c r="E51">
-        <v>4.8</v>
-      </c>
-      <c r="F51">
-        <v>7055</v>
-      </c>
-      <c r="G51" t="s">
-        <v>203</v>
-      </c>
-      <c r="I51" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A52" t="s">
-        <v>204</v>
-      </c>
-      <c r="B52" t="s">
-        <v>205</v>
-      </c>
-      <c r="C52" t="s">
-        <v>206</v>
-      </c>
-      <c r="E52">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="F52">
-        <v>1046</v>
-      </c>
-      <c r="G52" t="s">
-        <v>207</v>
-      </c>
-      <c r="I52" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A53" t="s">
-        <v>214</v>
-      </c>
-      <c r="B53" t="s">
-        <v>215</v>
-      </c>
-      <c r="C53" t="s">
-        <v>216</v>
-      </c>
-      <c r="D53" t="s">
-        <v>217</v>
-      </c>
-      <c r="E53">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="F53">
-        <v>1619</v>
-      </c>
-      <c r="G53" t="s">
-        <v>218</v>
-      </c>
-      <c r="I53" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A54" t="s">
-        <v>225</v>
-      </c>
-      <c r="B54" t="s">
-        <v>226</v>
-      </c>
-      <c r="C54" t="s">
-        <v>227</v>
-      </c>
-      <c r="D54" t="s">
-        <v>228</v>
-      </c>
-      <c r="E54">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="F54">
-        <v>1392</v>
-      </c>
-      <c r="G54" t="s">
-        <v>229</v>
-      </c>
-      <c r="I54" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A55" t="s">
-        <v>230</v>
-      </c>
-      <c r="B55" t="s">
-        <v>231</v>
-      </c>
-      <c r="C55" t="s">
-        <v>232</v>
-      </c>
-      <c r="D55" t="s">
-        <v>233</v>
-      </c>
-      <c r="E55">
-        <v>4.7</v>
-      </c>
-      <c r="F55">
-        <v>12011</v>
-      </c>
-      <c r="G55" t="s">
-        <v>234</v>
-      </c>
-      <c r="I55" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A56" t="s">
-        <v>235</v>
-      </c>
-      <c r="B56" t="s">
-        <v>236</v>
-      </c>
-      <c r="C56" t="s">
-        <v>237</v>
-      </c>
-      <c r="D56" t="s">
-        <v>233</v>
-      </c>
-      <c r="E56">
-        <v>4.8</v>
-      </c>
-      <c r="F56">
-        <v>16811</v>
-      </c>
-      <c r="G56" t="s">
-        <v>238</v>
-      </c>
-      <c r="I56" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A57" t="s">
-        <v>239</v>
-      </c>
-      <c r="B57" t="s">
-        <v>240</v>
-      </c>
-      <c r="C57" t="s">
-        <v>241</v>
-      </c>
-      <c r="D57" t="s">
-        <v>242</v>
-      </c>
-      <c r="E57">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="F57">
-        <v>1888</v>
-      </c>
-      <c r="G57" t="s">
-        <v>243</v>
-      </c>
-      <c r="I57" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A58" t="s">
-        <v>256</v>
-      </c>
-      <c r="B58" t="s">
-        <v>257</v>
-      </c>
-      <c r="C58" t="s">
-        <v>258</v>
-      </c>
-      <c r="D58" t="s">
-        <v>259</v>
-      </c>
-      <c r="E58">
-        <v>4.3</v>
-      </c>
-      <c r="F58">
-        <v>2252</v>
-      </c>
-      <c r="G58" t="s">
-        <v>260</v>
-      </c>
-      <c r="I58" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A59" t="s">
-        <v>261</v>
-      </c>
-      <c r="B59" t="s">
-        <v>262</v>
-      </c>
-      <c r="C59" t="s">
-        <v>263</v>
-      </c>
-      <c r="D59" t="s">
-        <v>264</v>
-      </c>
-      <c r="E59">
-        <v>4.5</v>
-      </c>
-      <c r="F59">
-        <v>1335</v>
-      </c>
-      <c r="G59" t="s">
-        <v>265</v>
-      </c>
-      <c r="I59" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A60" t="s">
-        <v>266</v>
-      </c>
-      <c r="B60" t="s">
-        <v>267</v>
-      </c>
-      <c r="C60" t="s">
-        <v>268</v>
-      </c>
-      <c r="D60" t="s">
-        <v>228</v>
-      </c>
-      <c r="E60">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="F60">
-        <v>1107</v>
-      </c>
-      <c r="G60" t="s">
-        <v>269</v>
-      </c>
-      <c r="I60" t="s">
-        <v>14</v>
-      </c>
-    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I60">
-    <sortCondition ref="I2:I60"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I47">
+    <sortCondition ref="I2:I47"/>
   </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/restaurant_crawler/restaurant_data_台北_牛排_20250910_192841_with_emails.xlsx
+++ b/restaurant_crawler/restaurant_data_台北_牛排_20250910_192841_with_emails.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\slow3\OneDrive\桌面\GitHubProjects\BYOB\restaurant_crawler\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32206034-F938-45BD-9C2E-59940CEF9B28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCB5693D-04EE-4199-813C-49AF3EB890D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="205">
   <si>
     <t>name</t>
   </si>
@@ -373,45 +373,6 @@
     <t>jencongzhong@gmail.com</t>
   </si>
   <si>
-    <t>【星辰牛排】</t>
-  </si>
-  <si>
-    <t>106台灣台北市大安區光復南路180巷16號</t>
-  </si>
-  <si>
-    <t>02 2721 7512</t>
-  </si>
-  <si>
-    <t>ChIJBa8s4carQjQRB2u8bcDiRMo</t>
-  </si>
-  <si>
-    <t>紅屋牛排館民生店</t>
-  </si>
-  <si>
-    <t>105台灣台北市松山區民生東路三段119號</t>
-  </si>
-  <si>
-    <t>02 2719 5167</t>
-  </si>
-  <si>
-    <t>https://www.homesteak.com.tw/</t>
-  </si>
-  <si>
-    <t>ChIJtxDpweWrQjQRtjMS9XTlMzo</t>
-  </si>
-  <si>
-    <t>王品牛排 台北羅斯福店</t>
-  </si>
-  <si>
-    <t>100台灣台北市中正區羅斯福路二段9號</t>
-  </si>
-  <si>
-    <t>02 2393 4689</t>
-  </si>
-  <si>
-    <t>ChIJwXTajYapQjQRiiVNmhlyrNk</t>
-  </si>
-  <si>
     <t>全家人牛排</t>
   </si>
   <si>
@@ -493,60 +454,6 @@
     <t>ChIJ5w-cntqrQjQRrRARHVKxABg</t>
   </si>
   <si>
-    <t>知名度牛排《訂位位置保留5分鐘》</t>
-  </si>
-  <si>
-    <t>235台灣新北市中和區忠孝街141號</t>
-  </si>
-  <si>
-    <t>02 3151 1026</t>
-  </si>
-  <si>
-    <t>https://instagram.com/dmd_141?igshid=1lvrllewuij9s</t>
-  </si>
-  <si>
-    <t>ChIJOXsF848DaDQRmsltV66ETmk</t>
-  </si>
-  <si>
-    <t>N°168 PRIME 敦化館</t>
-  </si>
-  <si>
-    <t>106台灣台北市大安區敦化南路1段246號7樓</t>
-  </si>
-  <si>
-    <t>02 6617 6168</t>
-  </si>
-  <si>
-    <t>https://grandvictoria.com.tw/dining/n168-prime-dunhua-store/</t>
-  </si>
-  <si>
-    <t>ChIJv5zxAdCrQjQRYpGCL-p9_zk</t>
-  </si>
-  <si>
-    <t>王品牛排 台北南京東店</t>
-  </si>
-  <si>
-    <t>105台灣台北市松山區南京東路四段169號</t>
-  </si>
-  <si>
-    <t>02 8770 7989</t>
-  </si>
-  <si>
-    <t>ChIJMc7_UeqrQjQRhsNKuTPuN9A</t>
-  </si>
-  <si>
-    <t>紅爐牛排館</t>
-  </si>
-  <si>
-    <t>100台灣台北市中正區仁愛路二段32號</t>
-  </si>
-  <si>
-    <t>02 2397 2368</t>
-  </si>
-  <si>
-    <t>ChIJVVVVVRWsQjQR-_9g3eZQXIU</t>
-  </si>
-  <si>
     <t>台北喜來登大飯店－安東廳 Antoine Room</t>
   </si>
   <si>
@@ -628,18 +535,6 @@
     <t>ChIJwdwRD9qrQjQR8v-5KSTMrpQ</t>
   </si>
   <si>
-    <t>西堤牛排 台北重慶南店</t>
-  </si>
-  <si>
-    <t>100台灣台北市中正區重慶南路一段129號2 樓</t>
-  </si>
-  <si>
-    <t>02 2370 8292</t>
-  </si>
-  <si>
-    <t>ChIJAfEkOgupQjQREzjn6Y_FME8</t>
-  </si>
-  <si>
     <t>凱薩西餐牛排</t>
   </si>
   <si>
@@ -704,33 +599,6 @@
   </si>
   <si>
     <t>ChIJA-dy15SrQjQRY85AKqSup6E</t>
-  </si>
-  <si>
-    <t>【台北君悅酒店】Bel Air 寶艾西餐廳</t>
-  </si>
-  <si>
-    <t>110061台灣台北市信义区松寿路2號2F</t>
-  </si>
-  <si>
-    <t>02 2720 1230</t>
-  </si>
-  <si>
-    <t>https://www.hyatt.com/zh-HK/hotel/taiwan/grand-hyatt-taipei/taigh/dining?src=prop_misc_taigh_other_google-my-business_belair</t>
-  </si>
-  <si>
-    <t>ChIJuS1ap7erQjQRFIt2P8e5H4s</t>
-  </si>
-  <si>
-    <t>Wayne’s New York 瑋恩紐約美式龍蝦牛排餐廳</t>
-  </si>
-  <si>
-    <t>110台灣台北市信義區基隆路二段81號</t>
-  </si>
-  <si>
-    <t>02 2377 9007</t>
-  </si>
-  <si>
-    <t>ChIJt7JDM4KrQjQRjbeuPqbQQ8A</t>
   </si>
   <si>
     <t>m</t>
@@ -757,13 +625,26 @@
   </si>
   <si>
     <t>taipei.ms@ruthschris.com.tw</t>
+  </si>
+  <si>
+    <t>maoinn1982@gmail.com</t>
+  </si>
+  <si>
+    <t>steak.henry@gmail.com</t>
+  </si>
+  <si>
+    <t>洽服務人員</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>marketing@tasty.com.tw</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -785,8 +666,14 @@
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Microsoft JhengHei"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -796,6 +683,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -827,12 +720,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -1135,8 +1031,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K47"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:K39"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="40.375" customWidth="1"/>
     <col min="4" max="4" width="46.25" customWidth="1"/>
@@ -1144,7 +1040,7 @@
     <col min="9" max="9" width="17.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1173,7 +1069,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9">
       <c r="A2" t="s">
         <v>20</v>
       </c>
@@ -1202,7 +1098,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9">
       <c r="A3" t="s">
         <v>27</v>
       </c>
@@ -1231,7 +1127,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9">
       <c r="A4" t="s">
         <v>53</v>
       </c>
@@ -1260,7 +1156,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9">
       <c r="A5" t="s">
         <v>59</v>
       </c>
@@ -1289,7 +1185,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9">
       <c r="A6" t="s">
         <v>75</v>
       </c>
@@ -1318,7 +1214,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9">
       <c r="A7" t="s">
         <v>111</v>
       </c>
@@ -1347,18 +1243,18 @@
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9">
       <c r="A8" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="B8" t="s">
-        <v>136</v>
+        <v>123</v>
       </c>
       <c r="C8" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>138</v>
+        <v>125</v>
       </c>
       <c r="E8">
         <v>4.5</v>
@@ -1367,27 +1263,27 @@
         <v>4412</v>
       </c>
       <c r="G8" t="s">
-        <v>139</v>
+        <v>126</v>
       </c>
       <c r="H8" t="s">
-        <v>140</v>
+        <v>127</v>
       </c>
       <c r="I8" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9">
       <c r="A9" t="s">
-        <v>146</v>
+        <v>133</v>
       </c>
       <c r="B9" t="s">
-        <v>147</v>
+        <v>134</v>
       </c>
       <c r="C9" t="s">
-        <v>148</v>
+        <v>135</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>149</v>
+        <v>136</v>
       </c>
       <c r="E9">
         <v>4.0999999999999996</v>
@@ -1396,27 +1292,27 @@
         <v>1657</v>
       </c>
       <c r="G9" t="s">
-        <v>150</v>
+        <v>137</v>
       </c>
       <c r="H9" t="s">
-        <v>151</v>
+        <v>138</v>
       </c>
       <c r="I9" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9">
       <c r="A10" t="s">
-        <v>175</v>
+        <v>144</v>
       </c>
       <c r="B10" t="s">
-        <v>176</v>
+        <v>145</v>
       </c>
       <c r="C10" t="s">
-        <v>177</v>
+        <v>146</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>178</v>
+        <v>147</v>
       </c>
       <c r="E10">
         <v>4.4000000000000004</v>
@@ -1425,27 +1321,27 @@
         <v>636</v>
       </c>
       <c r="G10" t="s">
-        <v>179</v>
+        <v>148</v>
       </c>
       <c r="H10" t="s">
-        <v>180</v>
+        <v>149</v>
       </c>
       <c r="I10" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9">
       <c r="A11" t="s">
-        <v>186</v>
+        <v>155</v>
       </c>
       <c r="B11" t="s">
-        <v>187</v>
+        <v>156</v>
       </c>
       <c r="C11" t="s">
-        <v>188</v>
+        <v>157</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>189</v>
+        <v>158</v>
       </c>
       <c r="E11">
         <v>4.0999999999999996</v>
@@ -1454,27 +1350,27 @@
         <v>2438</v>
       </c>
       <c r="G11" t="s">
-        <v>190</v>
+        <v>159</v>
       </c>
       <c r="H11" t="s">
-        <v>191</v>
+        <v>160</v>
       </c>
       <c r="I11" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9">
       <c r="A12" t="s">
-        <v>211</v>
+        <v>176</v>
       </c>
       <c r="B12" t="s">
-        <v>212</v>
+        <v>177</v>
       </c>
       <c r="C12" t="s">
-        <v>213</v>
+        <v>178</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>214</v>
+        <v>179</v>
       </c>
       <c r="E12">
         <v>4.2</v>
@@ -1483,27 +1379,27 @@
         <v>925</v>
       </c>
       <c r="G12" t="s">
-        <v>215</v>
+        <v>180</v>
       </c>
       <c r="H12" t="s">
-        <v>216</v>
+        <v>181</v>
       </c>
       <c r="I12" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9">
       <c r="A13" t="s">
-        <v>217</v>
+        <v>182</v>
       </c>
       <c r="B13" t="s">
-        <v>218</v>
+        <v>183</v>
       </c>
       <c r="C13" t="s">
-        <v>219</v>
+        <v>184</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>220</v>
+        <v>185</v>
       </c>
       <c r="E13">
         <v>4.0999999999999996</v>
@@ -1512,16 +1408,16 @@
         <v>1970</v>
       </c>
       <c r="G13" t="s">
-        <v>221</v>
+        <v>186</v>
       </c>
       <c r="H13" t="s">
-        <v>222</v>
+        <v>187</v>
       </c>
       <c r="I13" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9">
       <c r="A14" t="s">
         <v>43</v>
       </c>
@@ -1531,7 +1427,7 @@
       <c r="C14" t="s">
         <v>45</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D14" s="4" t="s">
         <v>46</v>
       </c>
       <c r="E14">
@@ -1544,13 +1440,13 @@
         <v>47</v>
       </c>
       <c r="H14" t="s">
-        <v>240</v>
+        <v>196</v>
       </c>
       <c r="I14" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9">
       <c r="A15" t="s">
         <v>15</v>
       </c>
@@ -1560,7 +1456,7 @@
       <c r="C15" t="s">
         <v>17</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D15" s="4" t="s">
         <v>18</v>
       </c>
       <c r="E15">
@@ -1573,13 +1469,13 @@
         <v>19</v>
       </c>
       <c r="H15" t="s">
-        <v>238</v>
+        <v>194</v>
       </c>
       <c r="I15" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9">
       <c r="A16" t="s">
         <v>48</v>
       </c>
@@ -1589,7 +1485,7 @@
       <c r="C16" t="s">
         <v>50</v>
       </c>
-      <c r="D16" t="s">
+      <c r="D16" s="4" t="s">
         <v>51</v>
       </c>
       <c r="E16">
@@ -1602,13 +1498,13 @@
         <v>52</v>
       </c>
       <c r="H16" t="s">
-        <v>241</v>
+        <v>197</v>
       </c>
       <c r="I16" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11">
       <c r="A17" t="s">
         <v>65</v>
       </c>
@@ -1618,7 +1514,7 @@
       <c r="C17" t="s">
         <v>67</v>
       </c>
-      <c r="D17" t="s">
+      <c r="D17" s="4" t="s">
         <v>68</v>
       </c>
       <c r="E17">
@@ -1631,13 +1527,13 @@
         <v>69</v>
       </c>
       <c r="H17" t="s">
-        <v>242</v>
+        <v>198</v>
       </c>
       <c r="I17" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11">
       <c r="A18" t="s">
         <v>70</v>
       </c>
@@ -1647,7 +1543,7 @@
       <c r="C18" t="s">
         <v>72</v>
       </c>
-      <c r="D18" t="s">
+      <c r="D18" s="4" t="s">
         <v>73</v>
       </c>
       <c r="E18">
@@ -1660,13 +1556,13 @@
         <v>74</v>
       </c>
       <c r="H18" t="s">
-        <v>243</v>
+        <v>199</v>
       </c>
       <c r="I18" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11">
       <c r="A19" t="s">
         <v>81</v>
       </c>
@@ -1676,7 +1572,7 @@
       <c r="C19" t="s">
         <v>83</v>
       </c>
-      <c r="D19" t="s">
+      <c r="D19" s="4" t="s">
         <v>84</v>
       </c>
       <c r="E19">
@@ -1689,694 +1585,458 @@
         <v>85</v>
       </c>
       <c r="H19" t="s">
-        <v>244</v>
+        <v>200</v>
       </c>
       <c r="I19" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:11">
+      <c r="A20" t="s">
+        <v>101</v>
+      </c>
+      <c r="B20" t="s">
+        <v>102</v>
+      </c>
+      <c r="C20" t="s">
+        <v>103</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="E20">
+        <v>4.7</v>
+      </c>
+      <c r="F20">
+        <v>487</v>
+      </c>
+      <c r="G20" t="s">
+        <v>105</v>
+      </c>
+      <c r="H20" t="s">
+        <v>201</v>
+      </c>
+      <c r="I20" t="s">
+        <v>14</v>
+      </c>
+      <c r="K20">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
+      <c r="A21" t="s">
+        <v>150</v>
+      </c>
+      <c r="B21" t="s">
+        <v>151</v>
+      </c>
+      <c r="C21" t="s">
+        <v>152</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="E21">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="F21">
+        <v>1619</v>
+      </c>
+      <c r="G21" t="s">
+        <v>154</v>
+      </c>
+      <c r="H21" t="s">
+        <v>202</v>
+      </c>
+      <c r="I21" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11">
       <c r="A22" t="s">
-        <v>9</v>
+        <v>166</v>
       </c>
       <c r="B22" t="s">
-        <v>10</v>
+        <v>167</v>
       </c>
       <c r="C22" t="s">
-        <v>11</v>
-      </c>
-      <c r="D22" t="s">
-        <v>12</v>
+        <v>168</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>169</v>
       </c>
       <c r="E22">
         <v>4.7</v>
       </c>
       <c r="F22">
+        <v>12011</v>
+      </c>
+      <c r="G22" t="s">
+        <v>170</v>
+      </c>
+      <c r="H22" t="s">
+        <v>204</v>
+      </c>
+      <c r="I22" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11">
+      <c r="D23" s="5"/>
+    </row>
+    <row r="27" spans="1:11">
+      <c r="A27" t="s">
+        <v>9</v>
+      </c>
+      <c r="B27" t="s">
+        <v>10</v>
+      </c>
+      <c r="C27" t="s">
+        <v>11</v>
+      </c>
+      <c r="D27" t="s">
+        <v>12</v>
+      </c>
+      <c r="E27">
+        <v>4.7</v>
+      </c>
+      <c r="F27">
         <v>11022</v>
       </c>
-      <c r="G22" t="s">
+      <c r="G27" t="s">
         <v>13</v>
       </c>
-      <c r="I22" t="s">
-        <v>14</v>
-      </c>
-      <c r="J22" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
+      <c r="I27" t="s">
+        <v>14</v>
+      </c>
+      <c r="J27" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11">
+      <c r="A28" t="s">
         <v>33</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B28" t="s">
         <v>34</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C28" t="s">
         <v>35</v>
       </c>
-      <c r="D23" t="s">
+      <c r="D28" t="s">
         <v>36</v>
       </c>
-      <c r="E23">
+      <c r="E28">
         <v>4.3</v>
       </c>
-      <c r="F23">
+      <c r="F28">
         <v>3659</v>
       </c>
-      <c r="G23" t="s">
+      <c r="G28" t="s">
         <v>37</v>
       </c>
-      <c r="I23" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
+      <c r="I28" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11">
+      <c r="A29" t="s">
         <v>38</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B29" t="s">
         <v>39</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C29" t="s">
         <v>40</v>
       </c>
-      <c r="D24" t="s">
+      <c r="D29" t="s">
         <v>41</v>
       </c>
-      <c r="E24">
+      <c r="E29">
         <v>4.3</v>
       </c>
-      <c r="F24">
+      <c r="F29">
         <v>3326</v>
       </c>
-      <c r="G24" t="s">
+      <c r="G29" t="s">
         <v>42</v>
       </c>
-      <c r="I24" t="s">
-        <v>14</v>
-      </c>
-      <c r="J24" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
+      <c r="I29" t="s">
+        <v>14</v>
+      </c>
+      <c r="J29" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11">
+      <c r="A30" t="s">
         <v>86</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B30" t="s">
         <v>87</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C30" t="s">
         <v>88</v>
       </c>
-      <c r="D25" t="s">
+      <c r="D30" t="s">
         <v>89</v>
       </c>
-      <c r="E25">
+      <c r="E30">
         <v>4.7</v>
       </c>
-      <c r="F25">
+      <c r="F30">
         <v>3317</v>
       </c>
-      <c r="G25" t="s">
+      <c r="G30" t="s">
         <v>90</v>
       </c>
-      <c r="I25" t="s">
-        <v>14</v>
-      </c>
-      <c r="K25">
+      <c r="I30" t="s">
+        <v>14</v>
+      </c>
+      <c r="K30">
         <v>100</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
+    <row r="31" spans="1:11">
+      <c r="A31" t="s">
         <v>91</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B31" t="s">
         <v>92</v>
       </c>
-      <c r="C26" t="s">
+      <c r="C31" t="s">
         <v>93</v>
       </c>
-      <c r="D26" t="s">
+      <c r="D31" t="s">
         <v>94</v>
       </c>
-      <c r="E26">
+      <c r="E31">
         <v>4.2</v>
       </c>
-      <c r="F26">
+      <c r="F31">
         <v>1712</v>
       </c>
-      <c r="G26" t="s">
+      <c r="G31" t="s">
         <v>95</v>
       </c>
-      <c r="I26" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
+      <c r="I31" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11">
+      <c r="A32" t="s">
         <v>96</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B32" t="s">
         <v>97</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C32" t="s">
         <v>98</v>
       </c>
-      <c r="D27" t="s">
+      <c r="D32" t="s">
         <v>99</v>
       </c>
-      <c r="E27">
+      <c r="E32">
         <v>4.5</v>
       </c>
-      <c r="F27">
+      <c r="F32">
         <v>5745</v>
       </c>
-      <c r="G27" t="s">
+      <c r="G32" t="s">
         <v>100</v>
       </c>
-      <c r="I27" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
-        <v>101</v>
-      </c>
-      <c r="B28" t="s">
-        <v>102</v>
-      </c>
-      <c r="C28" t="s">
-        <v>103</v>
-      </c>
-      <c r="D28" t="s">
-        <v>104</v>
-      </c>
-      <c r="E28">
+      <c r="I32" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11">
+      <c r="A33" t="s">
+        <v>106</v>
+      </c>
+      <c r="B33" t="s">
+        <v>107</v>
+      </c>
+      <c r="C33" t="s">
+        <v>108</v>
+      </c>
+      <c r="D33" t="s">
+        <v>109</v>
+      </c>
+      <c r="E33">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="F33">
+        <v>1992</v>
+      </c>
+      <c r="G33" t="s">
+        <v>110</v>
+      </c>
+      <c r="I33" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11">
+      <c r="A34" t="s">
+        <v>117</v>
+      </c>
+      <c r="B34" t="s">
+        <v>118</v>
+      </c>
+      <c r="C34" t="s">
+        <v>119</v>
+      </c>
+      <c r="D34" t="s">
+        <v>120</v>
+      </c>
+      <c r="E34">
+        <v>4.5</v>
+      </c>
+      <c r="F34">
+        <v>1467</v>
+      </c>
+      <c r="G34" t="s">
+        <v>121</v>
+      </c>
+      <c r="I34" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11">
+      <c r="A35" t="s">
+        <v>128</v>
+      </c>
+      <c r="B35" t="s">
+        <v>129</v>
+      </c>
+      <c r="C35" t="s">
+        <v>130</v>
+      </c>
+      <c r="D35" t="s">
+        <v>131</v>
+      </c>
+      <c r="E35">
         <v>4.7</v>
       </c>
-      <c r="F28">
-        <v>487</v>
-      </c>
-      <c r="G28" t="s">
-        <v>105</v>
-      </c>
-      <c r="I28" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
-        <v>106</v>
-      </c>
-      <c r="B29" t="s">
-        <v>107</v>
-      </c>
-      <c r="C29" t="s">
-        <v>108</v>
-      </c>
-      <c r="D29" t="s">
-        <v>109</v>
-      </c>
-      <c r="E29">
+      <c r="F35">
+        <v>88</v>
+      </c>
+      <c r="G35" t="s">
+        <v>132</v>
+      </c>
+      <c r="I35" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11">
+      <c r="A36" t="s">
+        <v>139</v>
+      </c>
+      <c r="B36" t="s">
+        <v>140</v>
+      </c>
+      <c r="C36" t="s">
+        <v>141</v>
+      </c>
+      <c r="D36" t="s">
+        <v>142</v>
+      </c>
+      <c r="E36">
         <v>4.4000000000000004</v>
       </c>
-      <c r="F29">
-        <v>1992</v>
-      </c>
-      <c r="G29" t="s">
-        <v>110</v>
-      </c>
-      <c r="I29" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
-        <v>117</v>
-      </c>
-      <c r="B30" t="s">
-        <v>118</v>
-      </c>
-      <c r="C30" t="s">
-        <v>119</v>
-      </c>
-      <c r="E30">
-        <v>4.5</v>
-      </c>
-      <c r="F30">
-        <v>3696</v>
-      </c>
-      <c r="G30" t="s">
-        <v>120</v>
-      </c>
-      <c r="I30" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
-        <v>121</v>
-      </c>
-      <c r="B31" t="s">
-        <v>122</v>
-      </c>
-      <c r="C31" t="s">
-        <v>123</v>
-      </c>
-      <c r="D31" t="s">
-        <v>124</v>
-      </c>
-      <c r="E31">
-        <v>4.5</v>
-      </c>
-      <c r="F31">
-        <v>2681</v>
-      </c>
-      <c r="G31" t="s">
-        <v>125</v>
-      </c>
-      <c r="I31" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
-        <v>126</v>
-      </c>
-      <c r="B32" t="s">
-        <v>127</v>
-      </c>
-      <c r="C32" t="s">
-        <v>128</v>
-      </c>
-      <c r="D32" t="s">
-        <v>73</v>
-      </c>
-      <c r="E32">
-        <v>4.8</v>
-      </c>
-      <c r="F32">
-        <v>8485</v>
-      </c>
-      <c r="G32" t="s">
-        <v>129</v>
-      </c>
-      <c r="I32" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
-        <v>130</v>
-      </c>
-      <c r="B33" t="s">
-        <v>131</v>
-      </c>
-      <c r="C33" t="s">
-        <v>132</v>
-      </c>
-      <c r="D33" t="s">
-        <v>133</v>
-      </c>
-      <c r="E33">
-        <v>4.5</v>
-      </c>
-      <c r="F33">
-        <v>1467</v>
-      </c>
-      <c r="G33" t="s">
-        <v>134</v>
-      </c>
-      <c r="I33" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
-        <v>141</v>
-      </c>
-      <c r="B34" t="s">
-        <v>142</v>
-      </c>
-      <c r="C34" t="s">
+      <c r="F36">
+        <v>1516</v>
+      </c>
+      <c r="G36" t="s">
         <v>143</v>
       </c>
-      <c r="D34" t="s">
-        <v>144</v>
-      </c>
-      <c r="E34">
-        <v>4.7</v>
-      </c>
-      <c r="F34">
-        <v>88</v>
-      </c>
-      <c r="G34" t="s">
-        <v>145</v>
-      </c>
-      <c r="I34" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
-        <v>152</v>
-      </c>
-      <c r="B35" t="s">
-        <v>153</v>
-      </c>
-      <c r="C35" t="s">
-        <v>154</v>
-      </c>
-      <c r="D35" t="s">
-        <v>155</v>
-      </c>
-      <c r="E35">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="F35">
-        <v>1516</v>
-      </c>
-      <c r="G35" t="s">
-        <v>156</v>
-      </c>
-      <c r="I35" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
-        <v>157</v>
-      </c>
-      <c r="B36" t="s">
-        <v>158</v>
-      </c>
-      <c r="C36" t="s">
-        <v>159</v>
-      </c>
-      <c r="D36" t="s">
-        <v>160</v>
-      </c>
-      <c r="E36">
-        <v>4.3</v>
-      </c>
-      <c r="F36">
-        <v>820</v>
-      </c>
-      <c r="G36" t="s">
+      <c r="I36" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11">
+      <c r="A37" t="s">
         <v>161</v>
       </c>
-      <c r="I36" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
+      <c r="B37" t="s">
         <v>162</v>
       </c>
-      <c r="B37" t="s">
+      <c r="C37" t="s">
         <v>163</v>
       </c>
-      <c r="C37" t="s">
+      <c r="D37" t="s">
         <v>164</v>
-      </c>
-      <c r="D37" t="s">
-        <v>165</v>
       </c>
       <c r="E37">
         <v>4.4000000000000004</v>
       </c>
       <c r="F37">
-        <v>1242</v>
+        <v>1392</v>
       </c>
       <c r="G37" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I37" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="K37" s="3" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11">
       <c r="A38" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="B38" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="C38" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="D38" t="s">
-        <v>73</v>
+        <v>174</v>
       </c>
       <c r="E38">
-        <v>4.8</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="F38">
-        <v>7055</v>
+        <v>1888</v>
       </c>
       <c r="G38" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="I38" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:11">
       <c r="A39" t="s">
-        <v>171</v>
+        <v>188</v>
       </c>
       <c r="B39" t="s">
-        <v>172</v>
+        <v>189</v>
       </c>
       <c r="C39" t="s">
-        <v>173</v>
+        <v>190</v>
+      </c>
+      <c r="D39" t="s">
+        <v>191</v>
       </c>
       <c r="E39">
-        <v>4.4000000000000004</v>
+        <v>4.3</v>
       </c>
       <c r="F39">
-        <v>1046</v>
+        <v>2252</v>
       </c>
       <c r="G39" t="s">
-        <v>174</v>
+        <v>192</v>
       </c>
       <c r="I39" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
-        <v>181</v>
-      </c>
-      <c r="B40" t="s">
-        <v>182</v>
-      </c>
-      <c r="C40" t="s">
-        <v>183</v>
-      </c>
-      <c r="D40" t="s">
-        <v>184</v>
-      </c>
-      <c r="E40">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="F40">
-        <v>1619</v>
-      </c>
-      <c r="G40" t="s">
-        <v>185</v>
-      </c>
-      <c r="I40" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
-        <v>192</v>
-      </c>
-      <c r="B41" t="s">
-        <v>193</v>
-      </c>
-      <c r="C41" t="s">
-        <v>194</v>
-      </c>
-      <c r="D41" t="s">
-        <v>195</v>
-      </c>
-      <c r="E41">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="F41">
-        <v>1392</v>
-      </c>
-      <c r="G41" t="s">
-        <v>196</v>
-      </c>
-      <c r="I41" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
-        <v>197</v>
-      </c>
-      <c r="B42" t="s">
-        <v>198</v>
-      </c>
-      <c r="C42" t="s">
-        <v>199</v>
-      </c>
-      <c r="D42" t="s">
-        <v>200</v>
-      </c>
-      <c r="E42">
-        <v>4.7</v>
-      </c>
-      <c r="F42">
-        <v>12011</v>
-      </c>
-      <c r="G42" t="s">
-        <v>201</v>
-      </c>
-      <c r="I42" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
-        <v>202</v>
-      </c>
-      <c r="B43" t="s">
-        <v>203</v>
-      </c>
-      <c r="C43" t="s">
-        <v>204</v>
-      </c>
-      <c r="D43" t="s">
-        <v>200</v>
-      </c>
-      <c r="E43">
-        <v>4.8</v>
-      </c>
-      <c r="F43">
-        <v>16811</v>
-      </c>
-      <c r="G43" t="s">
-        <v>205</v>
-      </c>
-      <c r="I43" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
-        <v>206</v>
-      </c>
-      <c r="B44" t="s">
-        <v>207</v>
-      </c>
-      <c r="C44" t="s">
-        <v>208</v>
-      </c>
-      <c r="D44" t="s">
-        <v>209</v>
-      </c>
-      <c r="E44">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="F44">
-        <v>1888</v>
-      </c>
-      <c r="G44" t="s">
-        <v>210</v>
-      </c>
-      <c r="I44" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
-        <v>223</v>
-      </c>
-      <c r="B45" t="s">
-        <v>224</v>
-      </c>
-      <c r="C45" t="s">
-        <v>225</v>
-      </c>
-      <c r="D45" t="s">
-        <v>226</v>
-      </c>
-      <c r="E45">
-        <v>4.3</v>
-      </c>
-      <c r="F45">
-        <v>2252</v>
-      </c>
-      <c r="G45" t="s">
-        <v>227</v>
-      </c>
-      <c r="I45" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
-        <v>228</v>
-      </c>
-      <c r="B46" t="s">
-        <v>229</v>
-      </c>
-      <c r="C46" t="s">
-        <v>230</v>
-      </c>
-      <c r="D46" t="s">
-        <v>231</v>
-      </c>
-      <c r="E46">
-        <v>4.5</v>
-      </c>
-      <c r="F46">
-        <v>1335</v>
-      </c>
-      <c r="G46" t="s">
-        <v>232</v>
-      </c>
-      <c r="I46" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
-        <v>233</v>
-      </c>
-      <c r="B47" t="s">
-        <v>234</v>
-      </c>
-      <c r="C47" t="s">
-        <v>235</v>
-      </c>
-      <c r="D47" t="s">
-        <v>195</v>
-      </c>
-      <c r="E47">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="F47">
-        <v>1107</v>
-      </c>
-      <c r="G47" t="s">
-        <v>236</v>
-      </c>
-      <c r="I47" t="s">
-        <v>14</v>
-      </c>
-    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I47">
-    <sortCondition ref="I2:I47"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I39">
+    <sortCondition ref="I2:I39"/>
   </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/restaurant_crawler/restaurant_data_台北_牛排_20250910_192841_with_emails.xlsx
+++ b/restaurant_crawler/restaurant_data_台北_牛排_20250910_192841_with_emails.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\slow3\OneDrive\桌面\GitHubProjects\BYOB\restaurant_crawler\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCB5693D-04EE-4199-813C-49AF3EB890D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55AE4AA7-B9E0-45C8-BD53-003768C52D3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="207">
   <si>
     <t>name</t>
   </si>
@@ -638,6 +638,13 @@
   </si>
   <si>
     <t>marketing@tasty.com.tw</t>
+  </si>
+  <si>
+    <t>https://www.swiio.com/contact</t>
+  </si>
+  <si>
+    <t>Le Blanc</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -720,7 +727,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -728,7 +735,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -1031,7 +1037,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K39"/>
+  <dimension ref="A1:K40"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="40.375" customWidth="1"/>
@@ -1681,9 +1687,6 @@
         <v>14</v>
       </c>
     </row>
-    <row r="23" spans="1:11">
-      <c r="D23" s="5"/>
-    </row>
     <row r="27" spans="1:11">
       <c r="A27" t="s">
         <v>9</v>
@@ -2032,6 +2035,14 @@
       </c>
       <c r="I39" t="s">
         <v>14</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11">
+      <c r="A40" t="s">
+        <v>206</v>
+      </c>
+      <c r="D40" t="s">
+        <v>205</v>
       </c>
     </row>
   </sheetData>

--- a/restaurant_crawler/restaurant_data_台北_牛排_20250910_192841_with_emails.xlsx
+++ b/restaurant_crawler/restaurant_data_台北_牛排_20250910_192841_with_emails.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\slow3\OneDrive\桌面\GitHubProjects\BYOB\restaurant_crawler\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55AE4AA7-B9E0-45C8-BD53-003768C52D3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF557CBE-ACFA-4027-9BF5-BF7FE7DF84AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="203">
   <si>
     <t>name</t>
   </si>
@@ -119,21 +119,6 @@
   </si>
   <si>
     <t>customerservice@regenthotelsgroup.com</t>
-  </si>
-  <si>
-    <t>雅室牛排 仁愛圓環店</t>
-  </si>
-  <si>
-    <t>106台灣台北市大安區仁愛路四段105巷1號</t>
-  </si>
-  <si>
-    <t>02 2775 3011</t>
-  </si>
-  <si>
-    <t>https://linktr.ee/steakinn</t>
-  </si>
-  <si>
-    <t>ChIJGzqUC8-rQjQR8d5fRKpaNQo</t>
   </si>
   <si>
     <t>勞瑞斯牛肋排餐廳</t>
@@ -644,6 +629,10 @@
   </si>
   <si>
     <t>Le Blanc</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>m</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1037,7 +1026,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K40"/>
+  <dimension ref="A1:K39"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="40.375" customWidth="1"/>
@@ -1135,16 +1124,16 @@
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="B4" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="C4" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="E4">
         <v>4.5999999999999996</v>
@@ -1153,10 +1142,10 @@
         <v>6738</v>
       </c>
       <c r="G4" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="H4" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="I4" t="s">
         <v>26</v>
@@ -1164,16 +1153,16 @@
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="B5" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="C5" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="E5">
         <v>4.5</v>
@@ -1182,10 +1171,10 @@
         <v>1771</v>
       </c>
       <c r="G5" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="H5" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="I5" t="s">
         <v>26</v>
@@ -1193,16 +1182,16 @@
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B6" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="C6" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="E6">
         <v>4.2</v>
@@ -1211,10 +1200,10 @@
         <v>4469</v>
       </c>
       <c r="G6" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="H6" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="I6" t="s">
         <v>26</v>
@@ -1222,16 +1211,16 @@
     </row>
     <row r="7" spans="1:9">
       <c r="A7" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="B7" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="C7" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="E7">
         <v>4.3</v>
@@ -1240,10 +1229,10 @@
         <v>2018</v>
       </c>
       <c r="G7" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="H7" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="I7" t="s">
         <v>26</v>
@@ -1251,16 +1240,16 @@
     </row>
     <row r="8" spans="1:9">
       <c r="A8" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="B8" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="C8" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="E8">
         <v>4.5</v>
@@ -1269,10 +1258,10 @@
         <v>4412</v>
       </c>
       <c r="G8" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="H8" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="I8" t="s">
         <v>26</v>
@@ -1280,16 +1269,16 @@
     </row>
     <row r="9" spans="1:9">
       <c r="A9" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="B9" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="C9" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="E9">
         <v>4.0999999999999996</v>
@@ -1298,10 +1287,10 @@
         <v>1657</v>
       </c>
       <c r="G9" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="H9" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="I9" t="s">
         <v>26</v>
@@ -1309,16 +1298,16 @@
     </row>
     <row r="10" spans="1:9">
       <c r="A10" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="B10" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="C10" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="E10">
         <v>4.4000000000000004</v>
@@ -1327,10 +1316,10 @@
         <v>636</v>
       </c>
       <c r="G10" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="H10" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="I10" t="s">
         <v>26</v>
@@ -1338,16 +1327,16 @@
     </row>
     <row r="11" spans="1:9">
       <c r="A11" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="B11" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="C11" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="E11">
         <v>4.0999999999999996</v>
@@ -1356,10 +1345,10 @@
         <v>2438</v>
       </c>
       <c r="G11" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="H11" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="I11" t="s">
         <v>26</v>
@@ -1367,16 +1356,16 @@
     </row>
     <row r="12" spans="1:9">
       <c r="A12" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="B12" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="C12" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="E12">
         <v>4.2</v>
@@ -1385,10 +1374,10 @@
         <v>925</v>
       </c>
       <c r="G12" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="H12" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="I12" t="s">
         <v>26</v>
@@ -1396,16 +1385,16 @@
     </row>
     <row r="13" spans="1:9">
       <c r="A13" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="B13" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="C13" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="E13">
         <v>4.0999999999999996</v>
@@ -1414,10 +1403,10 @@
         <v>1970</v>
       </c>
       <c r="G13" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="H13" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="I13" t="s">
         <v>26</v>
@@ -1425,16 +1414,16 @@
     </row>
     <row r="14" spans="1:9">
       <c r="A14" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B14" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="C14" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E14">
         <v>4.5</v>
@@ -1443,10 +1432,10 @@
         <v>2399</v>
       </c>
       <c r="G14" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="H14" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="I14" t="s">
         <v>14</v>
@@ -1475,7 +1464,7 @@
         <v>19</v>
       </c>
       <c r="H15" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="I15" t="s">
         <v>14</v>
@@ -1483,16 +1472,16 @@
     </row>
     <row r="16" spans="1:9">
       <c r="A16" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="B16" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="C16" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="E16">
         <v>4.4000000000000004</v>
@@ -1501,10 +1490,10 @@
         <v>959</v>
       </c>
       <c r="G16" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="H16" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="I16" t="s">
         <v>14</v>
@@ -1512,16 +1501,16 @@
     </row>
     <row r="17" spans="1:11">
       <c r="A17" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="B17" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="C17" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="E17">
         <v>4.5</v>
@@ -1530,10 +1519,10 @@
         <v>5505</v>
       </c>
       <c r="G17" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="H17" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="I17" t="s">
         <v>14</v>
@@ -1541,16 +1530,16 @@
     </row>
     <row r="18" spans="1:11">
       <c r="A18" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="B18" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="C18" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="E18">
         <v>4.8</v>
@@ -1559,10 +1548,10 @@
         <v>11160</v>
       </c>
       <c r="G18" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="H18" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="I18" t="s">
         <v>14</v>
@@ -1570,16 +1559,16 @@
     </row>
     <row r="19" spans="1:11">
       <c r="A19" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="B19" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="C19" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="E19">
         <v>4.4000000000000004</v>
@@ -1588,10 +1577,10 @@
         <v>3517</v>
       </c>
       <c r="G19" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="H19" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="I19" t="s">
         <v>14</v>
@@ -1599,16 +1588,16 @@
     </row>
     <row r="20" spans="1:11">
       <c r="A20" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="B20" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="C20" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="E20">
         <v>4.7</v>
@@ -1617,10 +1606,10 @@
         <v>487</v>
       </c>
       <c r="G20" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="H20" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="I20" t="s">
         <v>14</v>
@@ -1631,16 +1620,16 @@
     </row>
     <row r="21" spans="1:11">
       <c r="A21" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="B21" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="C21" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="E21">
         <v>4.4000000000000004</v>
@@ -1649,10 +1638,10 @@
         <v>1619</v>
       </c>
       <c r="G21" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="H21" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="I21" t="s">
         <v>14</v>
@@ -1660,16 +1649,16 @@
     </row>
     <row r="22" spans="1:11">
       <c r="A22" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="B22" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="C22" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="E22">
         <v>4.7</v>
@@ -1678,10 +1667,10 @@
         <v>12011</v>
       </c>
       <c r="G22" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="H22" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="I22" t="s">
         <v>14</v>
@@ -1713,7 +1702,7 @@
         <v>14</v>
       </c>
       <c r="J27" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -1733,7 +1722,7 @@
         <v>4.3</v>
       </c>
       <c r="F28">
-        <v>3659</v>
+        <v>3326</v>
       </c>
       <c r="G28" t="s">
         <v>37</v>
@@ -1741,34 +1730,37 @@
       <c r="I28" t="s">
         <v>14</v>
       </c>
+      <c r="J28" t="s">
+        <v>188</v>
+      </c>
     </row>
     <row r="29" spans="1:11">
       <c r="A29" t="s">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="B29" t="s">
-        <v>39</v>
+        <v>82</v>
       </c>
       <c r="C29" t="s">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="D29" t="s">
-        <v>41</v>
+        <v>84</v>
       </c>
       <c r="E29">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="F29">
-        <v>3326</v>
+        <v>3317</v>
       </c>
       <c r="G29" t="s">
-        <v>42</v>
+        <v>85</v>
       </c>
       <c r="I29" t="s">
         <v>14</v>
       </c>
-      <c r="J29" t="s">
-        <v>193</v>
+      <c r="K29">
+        <v>100</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -1785,19 +1777,16 @@
         <v>89</v>
       </c>
       <c r="E30">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="F30">
-        <v>3317</v>
+        <v>1712</v>
       </c>
       <c r="G30" t="s">
         <v>90</v>
       </c>
       <c r="I30" t="s">
         <v>14</v>
-      </c>
-      <c r="K30">
-        <v>100</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -1814,10 +1803,10 @@
         <v>94</v>
       </c>
       <c r="E31">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="F31">
-        <v>1712</v>
+        <v>5745</v>
       </c>
       <c r="G31" t="s">
         <v>95</v>
@@ -1828,25 +1817,25 @@
     </row>
     <row r="32" spans="1:11">
       <c r="A32" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="B32" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="C32" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="D32" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="E32">
-        <v>4.5</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="F32">
-        <v>5745</v>
+        <v>1992</v>
       </c>
       <c r="G32" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="I32" t="s">
         <v>14</v>
@@ -1854,25 +1843,25 @@
     </row>
     <row r="33" spans="1:11">
       <c r="A33" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="B33" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="C33" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="D33" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="E33">
-        <v>4.4000000000000004</v>
+        <v>4.5</v>
       </c>
       <c r="F33">
-        <v>1992</v>
+        <v>1467</v>
       </c>
       <c r="G33" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="I33" t="s">
         <v>14</v>
@@ -1880,25 +1869,25 @@
     </row>
     <row r="34" spans="1:11">
       <c r="A34" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="B34" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="C34" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="D34" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="E34">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="F34">
-        <v>1467</v>
+        <v>88</v>
       </c>
       <c r="G34" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="I34" t="s">
         <v>14</v>
@@ -1906,25 +1895,25 @@
     </row>
     <row r="35" spans="1:11">
       <c r="A35" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="B35" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="C35" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="D35" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="E35">
-        <v>4.7</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="F35">
-        <v>88</v>
+        <v>1516</v>
       </c>
       <c r="G35" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="I35" t="s">
         <v>14</v>
@@ -1932,80 +1921,80 @@
     </row>
     <row r="36" spans="1:11">
       <c r="A36" t="s">
-        <v>139</v>
+        <v>156</v>
       </c>
       <c r="B36" t="s">
-        <v>140</v>
+        <v>157</v>
       </c>
       <c r="C36" t="s">
-        <v>141</v>
+        <v>158</v>
       </c>
       <c r="D36" t="s">
-        <v>142</v>
+        <v>159</v>
       </c>
       <c r="E36">
         <v>4.4000000000000004</v>
       </c>
       <c r="F36">
-        <v>1516</v>
+        <v>1392</v>
       </c>
       <c r="G36" t="s">
-        <v>143</v>
+        <v>160</v>
       </c>
       <c r="I36" t="s">
         <v>14</v>
       </c>
+      <c r="K36" s="3" t="s">
+        <v>198</v>
+      </c>
     </row>
     <row r="37" spans="1:11">
       <c r="A37" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="B37" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="C37" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="D37" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="E37">
         <v>4.4000000000000004</v>
       </c>
       <c r="F37">
-        <v>1392</v>
+        <v>1888</v>
       </c>
       <c r="G37" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="I37" t="s">
         <v>14</v>
       </c>
-      <c r="K37" s="3" t="s">
-        <v>203</v>
-      </c>
     </row>
     <row r="38" spans="1:11">
       <c r="A38" t="s">
-        <v>171</v>
+        <v>183</v>
       </c>
       <c r="B38" t="s">
-        <v>172</v>
+        <v>184</v>
       </c>
       <c r="C38" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="D38" t="s">
-        <v>174</v>
+        <v>186</v>
       </c>
       <c r="E38">
-        <v>4.4000000000000004</v>
+        <v>4.3</v>
       </c>
       <c r="F38">
-        <v>1888</v>
+        <v>2252</v>
       </c>
       <c r="G38" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="I38" t="s">
         <v>14</v>
@@ -2013,41 +2002,18 @@
     </row>
     <row r="39" spans="1:11">
       <c r="A39" t="s">
-        <v>188</v>
-      </c>
-      <c r="B39" t="s">
-        <v>189</v>
-      </c>
-      <c r="C39" t="s">
-        <v>190</v>
+        <v>201</v>
       </c>
       <c r="D39" t="s">
-        <v>191</v>
-      </c>
-      <c r="E39">
-        <v>4.3</v>
-      </c>
-      <c r="F39">
-        <v>2252</v>
-      </c>
-      <c r="G39" t="s">
-        <v>192</v>
-      </c>
-      <c r="I39" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11">
-      <c r="A40" t="s">
-        <v>206</v>
-      </c>
-      <c r="D40" t="s">
-        <v>205</v>
+        <v>200</v>
+      </c>
+      <c r="J39" t="s">
+        <v>202</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I39">
-    <sortCondition ref="I2:I39"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I38">
+    <sortCondition ref="I2:I38"/>
   </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
